--- a/lot_01.xlsx
+++ b/lot_01.xlsx
@@ -14,11 +14,11 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Services de proximite" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Artisanat &amp; BTP'!$A$3:$J$10</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Beaute &amp; Bien-etre'!$A$3:$J$10</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Restauration'!$A$3:$J$10</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Automobile'!$A$3:$J$10</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Services de proximite'!$A$3:$J$10</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Artisanat &amp; BTP'!$A$3:$K$10</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Beaute &amp; Bien-etre'!$A$3:$K$10</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Restauration'!$A$3:$K$10</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Automobile'!$A$3:$K$10</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Services de proximite'!$A$3:$K$10</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -27,7 +27,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="11">
+  <fonts count="12">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -92,6 +92,12 @@
       <color rgb="0092400E"/>
       <sz val="11"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00111827"/>
+      <sz val="10"/>
+    </font>
   </fonts>
   <fills count="6">
     <fill>
@@ -147,7 +153,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -161,6 +167,9 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -186,6 +195,9 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -209,6 +221,9 @@
     </xf>
     <xf numFmtId="0" fontId="10" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -575,19 +590,20 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J10"/>
+  <dimension ref="A1:K10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
     <col width="26" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="6" customWidth="1" min="4" max="4"/>
-    <col width="9" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="4" max="4"/>
+    <col width="6" customWidth="1" min="5" max="5"/>
     <col width="9" customWidth="1" min="6" max="6"/>
-    <col width="11" customWidth="1" min="7" max="7"/>
-    <col width="8" customWidth="1" min="8" max="8"/>
-    <col width="20" customWidth="1" min="9" max="9"/>
-    <col width="62" customWidth="1" min="10" max="10"/>
+    <col width="9" customWidth="1" min="7" max="7"/>
+    <col width="11" customWidth="1" min="8" max="8"/>
+    <col width="8" customWidth="1" min="9" max="9"/>
+    <col width="20" customWidth="1" min="10" max="10"/>
+    <col width="62" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1" ht="34" customHeight="1">
@@ -600,7 +616,7 @@
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Classés du site le plus indéfendable au moins pire. « Laideur » = score de design daté ; « Ancien. » = signaux d'abandon.</t>
+          <t>Classés du site le plus indéfendable au moins pire. « Laideur » = score de design daté ; « Ancien. » = signaux d'abandon. « Zone » est le centre de recherche, pas l'adresse : la commune réelle n'est indiquée que lorsque le site l'affiche.</t>
         </is>
       </c>
     </row>
@@ -617,40 +633,45 @@
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>Ville</t>
+          <t>Zone de recherche</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
+          <t>Commune réelle</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
           <t>Dép.</t>
         </is>
       </c>
-      <c r="E3" s="3" t="inlineStr">
+      <c r="F3" s="3" t="inlineStr">
         <is>
           <t>Laideur</t>
         </is>
       </c>
-      <c r="F3" s="3" t="inlineStr">
+      <c r="G3" s="3" t="inlineStr">
         <is>
           <t>Ancien.</t>
         </is>
       </c>
-      <c r="G3" s="3" t="inlineStr">
+      <c r="H3" s="3" t="inlineStr">
         <is>
           <t>Responsive</t>
         </is>
       </c>
-      <c r="H3" s="3" t="inlineStr">
+      <c r="I3" s="3" t="inlineStr">
         <is>
           <t>HTTPS</t>
         </is>
       </c>
-      <c r="I3" s="3" t="inlineStr">
+      <c r="J3" s="3" t="inlineStr">
         <is>
           <t>Techno</t>
         </is>
       </c>
-      <c r="J3" s="3" t="inlineStr">
+      <c r="K3" s="3" t="inlineStr">
         <is>
           <t>Ce qui cloche</t>
         </is>
@@ -672,81 +693,83 @@
           <t>Lyon</t>
         </is>
       </c>
-      <c r="D4" s="7" t="inlineStr">
+      <c r="D4" s="7" t="inlineStr"/>
+      <c r="E4" s="8" t="inlineStr">
         <is>
           <t>69</t>
         </is>
       </c>
-      <c r="E4" s="8" t="n">
+      <c r="F4" s="9" t="n">
         <v>74</v>
       </c>
-      <c r="F4" s="7" t="n">
+      <c r="G4" s="8" t="n">
         <v>8</v>
       </c>
-      <c r="G4" s="9" t="inlineStr">
-        <is>
-          <t>non</t>
-        </is>
-      </c>
-      <c r="H4" s="9" t="inlineStr">
+      <c r="H4" s="10" t="inlineStr">
         <is>
           <t>non</t>
         </is>
       </c>
       <c r="I4" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>non</t>
         </is>
       </c>
       <c r="J4" s="11" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K4" s="12" t="inlineStr">
+        <is>
           <t>layout en tableaux (5) | balises &lt;font&gt; (1) | doctype ancien | non responsive | pas de @media | px uniquement | pas de flex/grid | pas de variables CSS | aucun radius/ombre</t>
         </is>
       </c>
     </row>
     <row r="5" ht="30" customHeight="1">
-      <c r="A5" s="12" t="inlineStr">
+      <c r="A5" s="13" t="inlineStr">
         <is>
           <t>petezki.fr</t>
         </is>
       </c>
-      <c r="B5" s="13" t="inlineStr">
+      <c r="B5" s="14" t="inlineStr">
         <is>
           <t>Petezki &amp; Fils</t>
         </is>
       </c>
-      <c r="C5" s="14" t="inlineStr">
+      <c r="C5" s="15" t="inlineStr">
         <is>
           <t>Lyon</t>
         </is>
       </c>
-      <c r="D5" s="15" t="inlineStr">
+      <c r="D5" s="16" t="inlineStr"/>
+      <c r="E5" s="17" t="inlineStr">
         <is>
           <t>69</t>
         </is>
       </c>
-      <c r="E5" s="8" t="n">
+      <c r="F5" s="9" t="n">
         <v>67</v>
       </c>
-      <c r="F5" s="15" t="n">
+      <c r="G5" s="17" t="n">
         <v>6</v>
       </c>
-      <c r="G5" s="16" t="inlineStr">
-        <is>
-          <t>non</t>
-        </is>
-      </c>
-      <c r="H5" s="17" t="inlineStr">
+      <c r="H5" s="18" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="I5" s="19" t="inlineStr">
         <is>
           <t>oui</t>
         </is>
       </c>
-      <c r="I5" s="18" t="inlineStr">
+      <c r="J5" s="20" t="inlineStr">
         <is>
           <t>macromedia dreamweaver 8</t>
         </is>
       </c>
-      <c r="J5" s="19" t="inlineStr">
+      <c r="K5" s="21" t="inlineStr">
         <is>
           <t>layout en tableaux (9) | doctype ancien | non responsive | images .gif | pas de @media | px uniquement | pas de flex/grid | pas de variables CSS | aucun radius/ombre</t>
         </is>
@@ -768,81 +791,83 @@
           <t>Rennes</t>
         </is>
       </c>
-      <c r="D6" s="7" t="inlineStr">
+      <c r="D6" s="7" t="inlineStr"/>
+      <c r="E6" s="8" t="inlineStr">
         <is>
           <t>35</t>
         </is>
       </c>
-      <c r="E6" s="8" t="n">
+      <c r="F6" s="9" t="n">
         <v>56</v>
       </c>
-      <c r="F6" s="7" t="n">
+      <c r="G6" s="8" t="n">
         <v>8</v>
       </c>
-      <c r="G6" s="9" t="inlineStr">
-        <is>
-          <t>non</t>
-        </is>
-      </c>
-      <c r="H6" s="20" t="inlineStr">
+      <c r="H6" s="10" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="I6" s="22" t="inlineStr">
         <is>
           <t>oui</t>
         </is>
       </c>
-      <c r="I6" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="J6" s="11" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K6" s="12" t="inlineStr">
+        <is>
           <t>balises &lt;font&gt; (13) | non responsive | pas de @media | pas de flex/grid | pas de variables CSS | CSS tres court (434B) | aucun radius/ombre</t>
         </is>
       </c>
     </row>
     <row r="7" ht="30" customHeight="1">
-      <c r="A7" s="12" t="inlineStr">
+      <c r="A7" s="13" t="inlineStr">
         <is>
           <t>atie-bat.fr</t>
         </is>
       </c>
-      <c r="B7" s="13" t="inlineStr">
+      <c r="B7" s="14" t="inlineStr">
         <is>
           <t>Atie Bat</t>
         </is>
       </c>
-      <c r="C7" s="14" t="inlineStr">
+      <c r="C7" s="15" t="inlineStr">
         <is>
           <t>Paris</t>
         </is>
       </c>
-      <c r="D7" s="15" t="inlineStr">
+      <c r="D7" s="16" t="inlineStr"/>
+      <c r="E7" s="17" t="inlineStr">
         <is>
           <t>75</t>
         </is>
       </c>
-      <c r="E7" s="8" t="n">
+      <c r="F7" s="9" t="n">
         <v>56</v>
       </c>
-      <c r="F7" s="15" t="n">
+      <c r="G7" s="17" t="n">
         <v>6</v>
       </c>
-      <c r="G7" s="16" t="inlineStr">
-        <is>
-          <t>non</t>
-        </is>
-      </c>
-      <c r="H7" s="17" t="inlineStr">
+      <c r="H7" s="18" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="I7" s="19" t="inlineStr">
         <is>
           <t>oui</t>
         </is>
       </c>
-      <c r="I7" s="18" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J7" s="19" t="inlineStr">
+      <c r="J7" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K7" s="21" t="inlineStr">
         <is>
           <t>balises &lt;font&gt; (2) | non responsive | pas de @media | pas de flex/grid | pas de variables CSS | CSS tres court (434B) | aucun radius/ombre</t>
         </is>
@@ -864,81 +889,83 @@
           <t>Toulouse</t>
         </is>
       </c>
-      <c r="D8" s="7" t="inlineStr">
+      <c r="D8" s="7" t="inlineStr"/>
+      <c r="E8" s="8" t="inlineStr">
         <is>
           <t>31</t>
         </is>
       </c>
-      <c r="E8" s="8" t="n">
+      <c r="F8" s="9" t="n">
         <v>56</v>
       </c>
-      <c r="F8" s="7" t="n">
+      <c r="G8" s="8" t="n">
         <v>6</v>
       </c>
-      <c r="G8" s="9" t="inlineStr">
-        <is>
-          <t>non</t>
-        </is>
-      </c>
-      <c r="H8" s="20" t="inlineStr">
+      <c r="H8" s="10" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="I8" s="22" t="inlineStr">
         <is>
           <t>oui</t>
         </is>
       </c>
-      <c r="I8" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="J8" s="11" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K8" s="12" t="inlineStr">
+        <is>
           <t>balises &lt;font&gt; (1) | non responsive | pas de @media | pas de flex/grid | pas de variables CSS | CSS tres court (434B) | aucun radius/ombre</t>
         </is>
       </c>
     </row>
     <row r="9" ht="30" customHeight="1">
-      <c r="A9" s="12" t="inlineStr">
+      <c r="A9" s="13" t="inlineStr">
         <is>
           <t>tech-plomberie.fr</t>
         </is>
       </c>
-      <c r="B9" s="13" t="inlineStr">
+      <c r="B9" s="14" t="inlineStr">
         <is>
           <t>Tec Plomberie</t>
         </is>
       </c>
-      <c r="C9" s="14" t="inlineStr">
+      <c r="C9" s="15" t="inlineStr">
         <is>
           <t>Orleans</t>
         </is>
       </c>
-      <c r="D9" s="15" t="inlineStr">
+      <c r="D9" s="16" t="inlineStr"/>
+      <c r="E9" s="17" t="inlineStr">
         <is>
           <t>45</t>
         </is>
       </c>
-      <c r="E9" s="8" t="n">
+      <c r="F9" s="9" t="n">
         <v>56</v>
       </c>
-      <c r="F9" s="15" t="n">
+      <c r="G9" s="17" t="n">
         <v>6</v>
       </c>
-      <c r="G9" s="16" t="inlineStr">
-        <is>
-          <t>non</t>
-        </is>
-      </c>
-      <c r="H9" s="17" t="inlineStr">
+      <c r="H9" s="18" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="I9" s="19" t="inlineStr">
         <is>
           <t>oui</t>
         </is>
       </c>
-      <c r="I9" s="18" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J9" s="19" t="inlineStr">
+      <c r="J9" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K9" s="21" t="inlineStr">
         <is>
           <t>balises &lt;font&gt; (3) | non responsive | pas de @media | pas de flex/grid | pas de variables CSS | CSS tres court (434B) | aucun radius/ombre</t>
         </is>
@@ -960,43 +987,44 @@
           <t>Nancy</t>
         </is>
       </c>
-      <c r="D10" s="7" t="inlineStr">
+      <c r="D10" s="7" t="inlineStr"/>
+      <c r="E10" s="8" t="inlineStr">
         <is>
           <t>54</t>
         </is>
       </c>
-      <c r="E10" s="8" t="n">
+      <c r="F10" s="9" t="n">
         <v>55</v>
       </c>
-      <c r="F10" s="7" t="n">
+      <c r="G10" s="8" t="n">
         <v>6</v>
       </c>
-      <c r="G10" s="9" t="inlineStr">
-        <is>
-          <t>non</t>
-        </is>
-      </c>
-      <c r="H10" s="20" t="inlineStr">
+      <c r="H10" s="10" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="I10" s="22" t="inlineStr">
         <is>
           <t>oui</t>
         </is>
       </c>
-      <c r="I10" s="10" t="inlineStr">
+      <c r="J10" s="11" t="inlineStr">
         <is>
           <t>joomla! - copyright (c) 2005 - 2006 open source matters. all</t>
         </is>
       </c>
-      <c r="J10" s="11" t="inlineStr">
+      <c r="K10" s="12" t="inlineStr">
         <is>
           <t>layout en tableaux (7) | doctype ancien | non responsive | pas de @media | pas de flex/grid | aucun radius/ombre</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:J10"/>
+  <autoFilter ref="A3:K10"/>
   <mergeCells count="2">
-    <mergeCell ref="A1:J1"/>
-    <mergeCell ref="A2:J2"/>
+    <mergeCell ref="A2:K2"/>
+    <mergeCell ref="A1:K1"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A4" r:id="rId1"/>
@@ -1017,19 +1045,20 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J10"/>
+  <dimension ref="A1:K10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
     <col width="26" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="6" customWidth="1" min="4" max="4"/>
-    <col width="9" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="4" max="4"/>
+    <col width="6" customWidth="1" min="5" max="5"/>
     <col width="9" customWidth="1" min="6" max="6"/>
-    <col width="11" customWidth="1" min="7" max="7"/>
-    <col width="8" customWidth="1" min="8" max="8"/>
-    <col width="20" customWidth="1" min="9" max="9"/>
-    <col width="62" customWidth="1" min="10" max="10"/>
+    <col width="9" customWidth="1" min="7" max="7"/>
+    <col width="11" customWidth="1" min="8" max="8"/>
+    <col width="8" customWidth="1" min="9" max="9"/>
+    <col width="20" customWidth="1" min="10" max="10"/>
+    <col width="62" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1" ht="34" customHeight="1">
@@ -1042,7 +1071,7 @@
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Classés du site le plus indéfendable au moins pire. « Laideur » = score de design daté ; « Ancien. » = signaux d'abandon.</t>
+          <t>Classés du site le plus indéfendable au moins pire. « Laideur » = score de design daté ; « Ancien. » = signaux d'abandon. « Zone » est le centre de recherche, pas l'adresse : la commune réelle n'est indiquée que lorsque le site l'affiche.</t>
         </is>
       </c>
     </row>
@@ -1059,40 +1088,45 @@
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>Ville</t>
+          <t>Zone de recherche</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
+          <t>Commune réelle</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
           <t>Dép.</t>
         </is>
       </c>
-      <c r="E3" s="3" t="inlineStr">
+      <c r="F3" s="3" t="inlineStr">
         <is>
           <t>Laideur</t>
         </is>
       </c>
-      <c r="F3" s="3" t="inlineStr">
+      <c r="G3" s="3" t="inlineStr">
         <is>
           <t>Ancien.</t>
         </is>
       </c>
-      <c r="G3" s="3" t="inlineStr">
+      <c r="H3" s="3" t="inlineStr">
         <is>
           <t>Responsive</t>
         </is>
       </c>
-      <c r="H3" s="3" t="inlineStr">
+      <c r="I3" s="3" t="inlineStr">
         <is>
           <t>HTTPS</t>
         </is>
       </c>
-      <c r="I3" s="3" t="inlineStr">
+      <c r="J3" s="3" t="inlineStr">
         <is>
           <t>Techno</t>
         </is>
       </c>
-      <c r="J3" s="3" t="inlineStr">
+      <c r="K3" s="3" t="inlineStr">
         <is>
           <t>Ce qui cloche</t>
         </is>
@@ -1114,81 +1148,83 @@
           <t>Lyon</t>
         </is>
       </c>
-      <c r="D4" s="7" t="inlineStr">
+      <c r="D4" s="7" t="inlineStr"/>
+      <c r="E4" s="8" t="inlineStr">
         <is>
           <t>69</t>
         </is>
       </c>
-      <c r="E4" s="8" t="n">
+      <c r="F4" s="9" t="n">
         <v>69</v>
       </c>
-      <c r="F4" s="7" t="n">
+      <c r="G4" s="8" t="n">
         <v>8</v>
       </c>
-      <c r="G4" s="9" t="inlineStr">
-        <is>
-          <t>non</t>
-        </is>
-      </c>
-      <c r="H4" s="20" t="inlineStr">
+      <c r="H4" s="10" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="I4" s="22" t="inlineStr">
         <is>
           <t>oui</t>
         </is>
       </c>
-      <c r="I4" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="J4" s="11" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K4" s="12" t="inlineStr">
+        <is>
           <t>layout en tableaux (9) | balises &lt;font&gt; (15) | sans doctype | non responsive | pas de @media | pas de flex/grid | pas de variables CSS | aucun radius/ombre</t>
         </is>
       </c>
     </row>
     <row r="5" ht="30" customHeight="1">
-      <c r="A5" s="12" t="inlineStr">
+      <c r="A5" s="13" t="inlineStr">
         <is>
           <t>ermontbienetre.fr</t>
         </is>
       </c>
-      <c r="B5" s="13" t="inlineStr">
+      <c r="B5" s="14" t="inlineStr">
         <is>
           <t>Esthétique et Massage de Bien-Être</t>
         </is>
       </c>
-      <c r="C5" s="14" t="inlineStr">
+      <c r="C5" s="15" t="inlineStr">
         <is>
           <t>Paris</t>
         </is>
       </c>
-      <c r="D5" s="15" t="inlineStr">
+      <c r="D5" s="16" t="inlineStr"/>
+      <c r="E5" s="17" t="inlineStr">
         <is>
           <t>75</t>
         </is>
       </c>
-      <c r="E5" s="8" t="n">
+      <c r="F5" s="9" t="n">
         <v>68</v>
       </c>
-      <c r="F5" s="15" t="n">
+      <c r="G5" s="17" t="n">
         <v>6</v>
       </c>
-      <c r="G5" s="16" t="inlineStr">
-        <is>
-          <t>non</t>
-        </is>
-      </c>
-      <c r="H5" s="17" t="inlineStr">
+      <c r="H5" s="18" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="I5" s="19" t="inlineStr">
         <is>
           <t>oui</t>
         </is>
       </c>
-      <c r="I5" s="18" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J5" s="19" t="inlineStr">
+      <c r="J5" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K5" s="21" t="inlineStr">
         <is>
           <t>layout en tableaux (8) | bgcolor= | doctype ancien | non responsive | gif de mise en page | images .gif | pas de @media | pas de flex/grid | aucun radius/ombre</t>
         </is>
@@ -1210,81 +1246,83 @@
           <t>Paris</t>
         </is>
       </c>
-      <c r="D6" s="7" t="inlineStr">
+      <c r="D6" s="7" t="inlineStr"/>
+      <c r="E6" s="8" t="inlineStr">
         <is>
           <t>75</t>
         </is>
       </c>
-      <c r="E6" s="8" t="n">
+      <c r="F6" s="9" t="n">
         <v>66</v>
       </c>
-      <c r="F6" s="7" t="n">
+      <c r="G6" s="8" t="n">
         <v>6</v>
       </c>
-      <c r="G6" s="9" t="inlineStr">
-        <is>
-          <t>non</t>
-        </is>
-      </c>
-      <c r="H6" s="20" t="inlineStr">
+      <c r="H6" s="10" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="I6" s="22" t="inlineStr">
         <is>
           <t>oui</t>
         </is>
       </c>
-      <c r="I6" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="J6" s="11" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K6" s="12" t="inlineStr">
+        <is>
           <t>bgcolor= | frameset | sans doctype | non responsive | pas de @media | px uniquement | pas de flex/grid | pas de variables CSS | aucun radius/ombre</t>
         </is>
       </c>
     </row>
     <row r="7" ht="30" customHeight="1">
-      <c r="A7" s="12" t="inlineStr">
+      <c r="A7" s="13" t="inlineStr">
         <is>
           <t>auxonglesdor.free.fr</t>
         </is>
       </c>
-      <c r="B7" s="13" t="inlineStr">
+      <c r="B7" s="14" t="inlineStr">
         <is>
           <t>Aux Ongles d'Or</t>
         </is>
       </c>
-      <c r="C7" s="14" t="inlineStr">
+      <c r="C7" s="15" t="inlineStr">
         <is>
           <t>Paris</t>
         </is>
       </c>
-      <c r="D7" s="15" t="inlineStr">
+      <c r="D7" s="16" t="inlineStr"/>
+      <c r="E7" s="17" t="inlineStr">
         <is>
           <t>75</t>
         </is>
       </c>
-      <c r="E7" s="8" t="n">
+      <c r="F7" s="9" t="n">
         <v>58</v>
       </c>
-      <c r="F7" s="15" t="n">
+      <c r="G7" s="17" t="n">
         <v>10</v>
       </c>
-      <c r="G7" s="16" t="inlineStr">
-        <is>
-          <t>non</t>
-        </is>
-      </c>
-      <c r="H7" s="16" t="inlineStr">
+      <c r="H7" s="18" t="inlineStr">
         <is>
           <t>non</t>
         </is>
       </c>
       <c r="I7" s="18" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J7" s="19" t="inlineStr">
+          <t>non</t>
+        </is>
+      </c>
+      <c r="J7" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K7" s="21" t="inlineStr">
         <is>
           <t>&lt;center&gt; | doctype ancien | non responsive | gif de mise en page | pas de @media | pas de flex/grid | pas de variables CSS | police vintage | aucun radius/ombre</t>
         </is>
@@ -1306,81 +1344,83 @@
           <t>Marseille</t>
         </is>
       </c>
-      <c r="D8" s="7" t="inlineStr">
+      <c r="D8" s="7" t="inlineStr"/>
+      <c r="E8" s="8" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="E8" s="8" t="n">
+      <c r="F8" s="9" t="n">
         <v>58</v>
       </c>
-      <c r="F8" s="7" t="n">
+      <c r="G8" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="G8" s="9" t="inlineStr">
-        <is>
-          <t>non</t>
-        </is>
-      </c>
-      <c r="H8" s="20" t="inlineStr">
+      <c r="H8" s="10" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="I8" s="22" t="inlineStr">
         <is>
           <t>oui</t>
         </is>
       </c>
-      <c r="I8" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="J8" s="11" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K8" s="12" t="inlineStr">
+        <is>
           <t>layout en tableaux (13) | doctype ancien | non responsive | pas de @media | pas de flex/grid | pas de variables CSS | aucun radius/ombre</t>
         </is>
       </c>
     </row>
     <row r="9" ht="30" customHeight="1">
-      <c r="A9" s="12" t="inlineStr">
+      <c r="A9" s="13" t="inlineStr">
         <is>
           <t>atelier-arnaud-marie-coiffeur.fr</t>
         </is>
       </c>
-      <c r="B9" s="13" t="inlineStr">
+      <c r="B9" s="14" t="inlineStr">
         <is>
           <t>Arnaud Marie</t>
         </is>
       </c>
-      <c r="C9" s="14" t="inlineStr">
+      <c r="C9" s="15" t="inlineStr">
         <is>
           <t>Paris</t>
         </is>
       </c>
-      <c r="D9" s="15" t="inlineStr">
+      <c r="D9" s="16" t="inlineStr"/>
+      <c r="E9" s="17" t="inlineStr">
         <is>
           <t>75</t>
         </is>
       </c>
-      <c r="E9" s="8" t="n">
+      <c r="F9" s="9" t="n">
         <v>56</v>
       </c>
-      <c r="F9" s="15" t="n">
+      <c r="G9" s="17" t="n">
         <v>6</v>
       </c>
-      <c r="G9" s="16" t="inlineStr">
-        <is>
-          <t>non</t>
-        </is>
-      </c>
-      <c r="H9" s="17" t="inlineStr">
+      <c r="H9" s="18" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="I9" s="19" t="inlineStr">
         <is>
           <t>oui</t>
         </is>
       </c>
-      <c r="I9" s="18" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J9" s="19" t="inlineStr">
+      <c r="J9" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K9" s="21" t="inlineStr">
         <is>
           <t>balises &lt;font&gt; (4) | non responsive | pas de @media | pas de flex/grid | pas de variables CSS | CSS tres court (434B) | aucun radius/ombre</t>
         </is>
@@ -1389,56 +1429,57 @@
     <row r="10" ht="30" customHeight="1">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>attitudecoiffure-studiom.fr</t>
+          <t>florentina-linea.fr</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>Attitude Coiffure</t>
+          <t>Florentina</t>
         </is>
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>Saint-Etienne</t>
-        </is>
-      </c>
-      <c r="D10" s="7" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
-      <c r="E10" s="8" t="n">
-        <v>56</v>
-      </c>
-      <c r="F10" s="7" t="n">
-        <v>6</v>
-      </c>
-      <c r="G10" s="9" t="inlineStr">
-        <is>
-          <t>non</t>
-        </is>
-      </c>
-      <c r="H10" s="20" t="inlineStr">
-        <is>
-          <t>oui</t>
+          <t>Nantes</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr"/>
+      <c r="E10" s="8" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="F10" s="23" t="n">
+        <v>47</v>
+      </c>
+      <c r="G10" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="H10" s="10" t="inlineStr">
+        <is>
+          <t>non</t>
         </is>
       </c>
       <c r="I10" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>non</t>
         </is>
       </c>
       <c r="J10" s="11" t="inlineStr">
         <is>
-          <t>balises &lt;font&gt; (3) | non responsive | pas de @media | pas de flex/grid | pas de variables CSS | CSS tres court (434B) | aucun radius/ombre</t>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K10" s="12" t="inlineStr">
+        <is>
+          <t>balises &lt;font&gt; (1) | non responsive | pas de @media | pas de flex/grid | pas de variables CSS</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:J10"/>
+  <autoFilter ref="A3:K10"/>
   <mergeCells count="2">
-    <mergeCell ref="A1:J1"/>
-    <mergeCell ref="A2:J2"/>
+    <mergeCell ref="A2:K2"/>
+    <mergeCell ref="A1:K1"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A4" r:id="rId1"/>
@@ -1459,19 +1500,20 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J10"/>
+  <dimension ref="A1:K10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
     <col width="26" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="6" customWidth="1" min="4" max="4"/>
-    <col width="9" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="4" max="4"/>
+    <col width="6" customWidth="1" min="5" max="5"/>
     <col width="9" customWidth="1" min="6" max="6"/>
-    <col width="11" customWidth="1" min="7" max="7"/>
-    <col width="8" customWidth="1" min="8" max="8"/>
-    <col width="20" customWidth="1" min="9" max="9"/>
-    <col width="62" customWidth="1" min="10" max="10"/>
+    <col width="9" customWidth="1" min="7" max="7"/>
+    <col width="11" customWidth="1" min="8" max="8"/>
+    <col width="8" customWidth="1" min="9" max="9"/>
+    <col width="20" customWidth="1" min="10" max="10"/>
+    <col width="62" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1" ht="34" customHeight="1">
@@ -1484,7 +1526,7 @@
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Classés du site le plus indéfendable au moins pire. « Laideur » = score de design daté ; « Ancien. » = signaux d'abandon.</t>
+          <t>Classés du site le plus indéfendable au moins pire. « Laideur » = score de design daté ; « Ancien. » = signaux d'abandon. « Zone » est le centre de recherche, pas l'adresse : la commune réelle n'est indiquée que lorsque le site l'affiche.</t>
         </is>
       </c>
     </row>
@@ -1501,40 +1543,45 @@
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>Ville</t>
+          <t>Zone de recherche</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
+          <t>Commune réelle</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
           <t>Dép.</t>
         </is>
       </c>
-      <c r="E3" s="3" t="inlineStr">
+      <c r="F3" s="3" t="inlineStr">
         <is>
           <t>Laideur</t>
         </is>
       </c>
-      <c r="F3" s="3" t="inlineStr">
+      <c r="G3" s="3" t="inlineStr">
         <is>
           <t>Ancien.</t>
         </is>
       </c>
-      <c r="G3" s="3" t="inlineStr">
+      <c r="H3" s="3" t="inlineStr">
         <is>
           <t>Responsive</t>
         </is>
       </c>
-      <c r="H3" s="3" t="inlineStr">
+      <c r="I3" s="3" t="inlineStr">
         <is>
           <t>HTTPS</t>
         </is>
       </c>
-      <c r="I3" s="3" t="inlineStr">
+      <c r="J3" s="3" t="inlineStr">
         <is>
           <t>Techno</t>
         </is>
       </c>
-      <c r="J3" s="3" t="inlineStr">
+      <c r="K3" s="3" t="inlineStr">
         <is>
           <t>Ce qui cloche</t>
         </is>
@@ -1556,81 +1603,83 @@
           <t>Toulouse</t>
         </is>
       </c>
-      <c r="D4" s="7" t="inlineStr">
+      <c r="D4" s="7" t="inlineStr"/>
+      <c r="E4" s="8" t="inlineStr">
         <is>
           <t>31</t>
         </is>
       </c>
-      <c r="E4" s="8" t="n">
+      <c r="F4" s="9" t="n">
         <v>60</v>
       </c>
-      <c r="F4" s="7" t="n">
+      <c r="G4" s="8" t="n">
         <v>6</v>
       </c>
-      <c r="G4" s="9" t="inlineStr">
-        <is>
-          <t>non</t>
-        </is>
-      </c>
-      <c r="H4" s="20" t="inlineStr">
+      <c r="H4" s="10" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="I4" s="22" t="inlineStr">
         <is>
           <t>oui</t>
         </is>
       </c>
-      <c r="I4" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="J4" s="11" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K4" s="12" t="inlineStr">
+        <is>
           <t>balises &lt;font&gt; (5) | non responsive | document.write | pas de @media | pas de flex/grid | pas de variables CSS | CSS tres court (3B) | aucun radius/ombre</t>
         </is>
       </c>
     </row>
     <row r="5" ht="30" customHeight="1">
-      <c r="A5" s="12" t="inlineStr">
+      <c r="A5" s="13" t="inlineStr">
         <is>
           <t>chezmario.fr</t>
         </is>
       </c>
-      <c r="B5" s="13" t="inlineStr">
+      <c r="B5" s="14" t="inlineStr">
         <is>
           <t>Chez Mario</t>
         </is>
       </c>
-      <c r="C5" s="14" t="inlineStr">
+      <c r="C5" s="15" t="inlineStr">
         <is>
           <t>Bordeaux</t>
         </is>
       </c>
-      <c r="D5" s="15" t="inlineStr">
+      <c r="D5" s="16" t="inlineStr"/>
+      <c r="E5" s="17" t="inlineStr">
         <is>
           <t>33</t>
         </is>
       </c>
-      <c r="E5" s="8" t="n">
+      <c r="F5" s="9" t="n">
         <v>58</v>
       </c>
-      <c r="F5" s="15" t="n">
+      <c r="G5" s="17" t="n">
         <v>5</v>
       </c>
-      <c r="G5" s="16" t="inlineStr">
-        <is>
-          <t>non</t>
-        </is>
-      </c>
-      <c r="H5" s="16" t="inlineStr">
+      <c r="H5" s="18" t="inlineStr">
         <is>
           <t>non</t>
         </is>
       </c>
       <c r="I5" s="18" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J5" s="19" t="inlineStr">
+          <t>non</t>
+        </is>
+      </c>
+      <c r="J5" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K5" s="21" t="inlineStr">
         <is>
           <t>layout en tableaux (4) | doctype ancien | non responsive | pas de @media | pas de flex/grid | pas de variables CSS | aucun radius/ombre</t>
         </is>
@@ -1652,81 +1701,83 @@
           <t>Toulouse</t>
         </is>
       </c>
-      <c r="D6" s="7" t="inlineStr">
+      <c r="D6" s="7" t="inlineStr"/>
+      <c r="E6" s="8" t="inlineStr">
         <is>
           <t>31</t>
         </is>
       </c>
-      <c r="E6" s="8" t="n">
+      <c r="F6" s="9" t="n">
         <v>57</v>
       </c>
-      <c r="F6" s="7" t="n">
+      <c r="G6" s="8" t="n">
         <v>6</v>
       </c>
-      <c r="G6" s="9" t="inlineStr">
-        <is>
-          <t>non</t>
-        </is>
-      </c>
-      <c r="H6" s="20" t="inlineStr">
+      <c r="H6" s="10" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="I6" s="22" t="inlineStr">
         <is>
           <t>oui</t>
         </is>
       </c>
-      <c r="I6" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="J6" s="11" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K6" s="12" t="inlineStr">
+        <is>
           <t>layout en tableaux (9) | balises &lt;font&gt; (32) | &lt;center&gt; | bgcolor= | sans doctype | non responsive | images .gif</t>
         </is>
       </c>
     </row>
     <row r="7" ht="30" customHeight="1">
-      <c r="A7" s="12" t="inlineStr">
+      <c r="A7" s="13" t="inlineStr">
         <is>
           <t>lechateausormiou.fr</t>
         </is>
       </c>
-      <c r="B7" s="13" t="inlineStr">
+      <c r="B7" s="14" t="inlineStr">
         <is>
           <t>Le Château Sormiou</t>
         </is>
       </c>
-      <c r="C7" s="14" t="inlineStr">
+      <c r="C7" s="15" t="inlineStr">
         <is>
           <t>Marseille</t>
         </is>
       </c>
-      <c r="D7" s="15" t="inlineStr">
+      <c r="D7" s="16" t="inlineStr"/>
+      <c r="E7" s="17" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="E7" s="21" t="n">
+      <c r="F7" s="23" t="n">
         <v>47</v>
       </c>
-      <c r="F7" s="15" t="n">
+      <c r="G7" s="17" t="n">
         <v>8</v>
       </c>
-      <c r="G7" s="16" t="inlineStr">
-        <is>
-          <t>non</t>
-        </is>
-      </c>
-      <c r="H7" s="16" t="inlineStr">
+      <c r="H7" s="18" t="inlineStr">
         <is>
           <t>non</t>
         </is>
       </c>
       <c r="I7" s="18" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J7" s="19" t="inlineStr">
+          <t>non</t>
+        </is>
+      </c>
+      <c r="J7" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K7" s="21" t="inlineStr">
         <is>
           <t>balises &lt;font&gt; (1) | non responsive | pas de @media | pas de flex/grid | pas de variables CSS</t>
         </is>
@@ -1748,81 +1799,87 @@
           <t>Paris</t>
         </is>
       </c>
-      <c r="D8" s="7" t="inlineStr">
+      <c r="D8" s="24" t="inlineStr">
+        <is>
+          <t>Draveil (91210)</t>
+        </is>
+      </c>
+      <c r="E8" s="8" t="inlineStr">
         <is>
           <t>75</t>
         </is>
       </c>
-      <c r="E8" s="21" t="n">
+      <c r="F8" s="23" t="n">
         <v>47</v>
       </c>
-      <c r="F8" s="7" t="n">
+      <c r="G8" s="8" t="n">
         <v>6</v>
       </c>
-      <c r="G8" s="9" t="inlineStr">
-        <is>
-          <t>non</t>
-        </is>
-      </c>
-      <c r="H8" s="20" t="inlineStr">
+      <c r="H8" s="10" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="I8" s="22" t="inlineStr">
         <is>
           <t>oui</t>
         </is>
       </c>
-      <c r="I8" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="J8" s="11" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K8" s="12" t="inlineStr">
+        <is>
           <t>layout en tableaux (29) | balises &lt;font&gt; (4) | &lt;center&gt; | non responsive | &lt;br&gt; en masse</t>
         </is>
       </c>
     </row>
     <row r="9" ht="30" customHeight="1">
-      <c r="A9" s="12" t="inlineStr">
+      <c r="A9" s="13" t="inlineStr">
         <is>
           <t>chapitre6.fr</t>
         </is>
       </c>
-      <c r="B9" s="13" t="inlineStr">
+      <c r="B9" s="14" t="inlineStr">
         <is>
           <t>Chapitre VI</t>
         </is>
       </c>
-      <c r="C9" s="14" t="inlineStr">
+      <c r="C9" s="15" t="inlineStr">
         <is>
           <t>Lille</t>
         </is>
       </c>
-      <c r="D9" s="15" t="inlineStr">
+      <c r="D9" s="16" t="inlineStr"/>
+      <c r="E9" s="17" t="inlineStr">
         <is>
           <t>59</t>
         </is>
       </c>
-      <c r="E9" s="21" t="n">
+      <c r="F9" s="23" t="n">
         <v>45</v>
       </c>
-      <c r="F9" s="15" t="n">
+      <c r="G9" s="17" t="n">
         <v>8</v>
       </c>
-      <c r="G9" s="16" t="inlineStr">
-        <is>
-          <t>non</t>
-        </is>
-      </c>
-      <c r="H9" s="16" t="inlineStr">
+      <c r="H9" s="18" t="inlineStr">
         <is>
           <t>non</t>
         </is>
       </c>
       <c r="I9" s="18" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J9" s="19" t="inlineStr">
+          <t>non</t>
+        </is>
+      </c>
+      <c r="J9" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K9" s="21" t="inlineStr">
         <is>
           <t>balises &lt;font&gt; (1) | bgcolor= | frameset | sans doctype | non responsive</t>
         </is>
@@ -1844,43 +1901,44 @@
           <t>Nice</t>
         </is>
       </c>
-      <c r="D10" s="7" t="inlineStr">
+      <c r="D10" s="7" t="inlineStr"/>
+      <c r="E10" s="8" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="E10" s="21" t="n">
+      <c r="F10" s="23" t="n">
         <v>45</v>
       </c>
-      <c r="F10" s="7" t="n">
+      <c r="G10" s="8" t="n">
         <v>6</v>
       </c>
-      <c r="G10" s="9" t="inlineStr">
-        <is>
-          <t>non</t>
-        </is>
-      </c>
-      <c r="H10" s="20" t="inlineStr">
+      <c r="H10" s="10" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="I10" s="22" t="inlineStr">
         <is>
           <t>oui</t>
         </is>
       </c>
-      <c r="I10" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="J10" s="11" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K10" s="12" t="inlineStr">
+        <is>
           <t>&lt;center&gt; | non responsive | pas de @media | pas de flex/grid | pas de variables CSS | aucun radius/ombre</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:J10"/>
+  <autoFilter ref="A3:K10"/>
   <mergeCells count="2">
-    <mergeCell ref="A1:J1"/>
-    <mergeCell ref="A2:J2"/>
+    <mergeCell ref="A2:K2"/>
+    <mergeCell ref="A1:K1"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A4" r:id="rId1"/>
@@ -1901,19 +1959,20 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J10"/>
+  <dimension ref="A1:K10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
     <col width="26" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="6" customWidth="1" min="4" max="4"/>
-    <col width="9" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="4" max="4"/>
+    <col width="6" customWidth="1" min="5" max="5"/>
     <col width="9" customWidth="1" min="6" max="6"/>
-    <col width="11" customWidth="1" min="7" max="7"/>
-    <col width="8" customWidth="1" min="8" max="8"/>
-    <col width="20" customWidth="1" min="9" max="9"/>
-    <col width="62" customWidth="1" min="10" max="10"/>
+    <col width="9" customWidth="1" min="7" max="7"/>
+    <col width="11" customWidth="1" min="8" max="8"/>
+    <col width="8" customWidth="1" min="9" max="9"/>
+    <col width="20" customWidth="1" min="10" max="10"/>
+    <col width="62" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1" ht="34" customHeight="1">
@@ -1926,7 +1985,7 @@
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Classés du site le plus indéfendable au moins pire. « Laideur » = score de design daté ; « Ancien. » = signaux d'abandon.</t>
+          <t>Classés du site le plus indéfendable au moins pire. « Laideur » = score de design daté ; « Ancien. » = signaux d'abandon. « Zone » est le centre de recherche, pas l'adresse : la commune réelle n'est indiquée que lorsque le site l'affiche.</t>
         </is>
       </c>
     </row>
@@ -1943,40 +2002,45 @@
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>Ville</t>
+          <t>Zone de recherche</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
+          <t>Commune réelle</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
           <t>Dép.</t>
         </is>
       </c>
-      <c r="E3" s="3" t="inlineStr">
+      <c r="F3" s="3" t="inlineStr">
         <is>
           <t>Laideur</t>
         </is>
       </c>
-      <c r="F3" s="3" t="inlineStr">
+      <c r="G3" s="3" t="inlineStr">
         <is>
           <t>Ancien.</t>
         </is>
       </c>
-      <c r="G3" s="3" t="inlineStr">
+      <c r="H3" s="3" t="inlineStr">
         <is>
           <t>Responsive</t>
         </is>
       </c>
-      <c r="H3" s="3" t="inlineStr">
+      <c r="I3" s="3" t="inlineStr">
         <is>
           <t>HTTPS</t>
         </is>
       </c>
-      <c r="I3" s="3" t="inlineStr">
+      <c r="J3" s="3" t="inlineStr">
         <is>
           <t>Techno</t>
         </is>
       </c>
-      <c r="J3" s="3" t="inlineStr">
+      <c r="K3" s="3" t="inlineStr">
         <is>
           <t>Ce qui cloche</t>
         </is>
@@ -1998,83 +2062,85 @@
           <t>Lyon</t>
         </is>
       </c>
-      <c r="D4" s="7" t="inlineStr">
+      <c r="D4" s="7" t="inlineStr"/>
+      <c r="E4" s="8" t="inlineStr">
         <is>
           <t>69</t>
         </is>
       </c>
-      <c r="E4" s="8" t="n">
+      <c r="F4" s="9" t="n">
         <v>82</v>
       </c>
-      <c r="F4" s="7" t="n">
+      <c r="G4" s="8" t="n">
         <v>10</v>
       </c>
-      <c r="G4" s="9" t="inlineStr">
-        <is>
-          <t>non</t>
-        </is>
-      </c>
-      <c r="H4" s="9" t="inlineStr">
+      <c r="H4" s="10" t="inlineStr">
         <is>
           <t>non</t>
         </is>
       </c>
       <c r="I4" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>non</t>
         </is>
       </c>
       <c r="J4" s="11" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K4" s="12" t="inlineStr">
+        <is>
           <t>layout en tableaux (5) | balises &lt;font&gt; (1) | doctype ancien | non responsive | gif de mise en page | images .gif | pas de @media | px uniquement | pas de flex/grid | pas de variables CSS | aucun radius/ombre</t>
         </is>
       </c>
     </row>
     <row r="5" ht="30" customHeight="1">
-      <c r="A5" s="12" t="inlineStr">
-        <is>
-          <t>api-france.com</t>
-        </is>
-      </c>
-      <c r="B5" s="13" t="inlineStr">
-        <is>
-          <t>Auto Parts International</t>
-        </is>
-      </c>
-      <c r="C5" s="14" t="inlineStr">
-        <is>
-          <t>Toulouse</t>
-        </is>
-      </c>
-      <c r="D5" s="15" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="E5" s="8" t="n">
+      <c r="A5" s="13" t="inlineStr">
+        <is>
+          <t>garage-laban-rouen.fr</t>
+        </is>
+      </c>
+      <c r="B5" s="14" t="inlineStr">
+        <is>
+          <t>Garage Laban</t>
+        </is>
+      </c>
+      <c r="C5" s="15" t="inlineStr">
+        <is>
+          <t>Rouen</t>
+        </is>
+      </c>
+      <c r="D5" s="16" t="inlineStr"/>
+      <c r="E5" s="17" t="inlineStr">
+        <is>
+          <t>76</t>
+        </is>
+      </c>
+      <c r="F5" s="9" t="n">
         <v>56</v>
       </c>
-      <c r="F5" s="15" t="n">
+      <c r="G5" s="17" t="n">
         <v>6</v>
       </c>
-      <c r="G5" s="16" t="inlineStr">
-        <is>
-          <t>non</t>
-        </is>
-      </c>
-      <c r="H5" s="17" t="inlineStr">
+      <c r="H5" s="18" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="I5" s="19" t="inlineStr">
         <is>
           <t>oui</t>
         </is>
       </c>
-      <c r="I5" s="18" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J5" s="19" t="inlineStr">
-        <is>
-          <t>balises &lt;font&gt; (15) | non responsive | pas de @media | pas de flex/grid | pas de variables CSS | CSS tres court (434B) | aucun radius/ombre</t>
+      <c r="J5" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K5" s="21" t="inlineStr">
+        <is>
+          <t>balises &lt;font&gt; (16) | non responsive | pas de @media | pas de flex/grid | pas de variables CSS | CSS tres court (434B) | aucun radius/ombre</t>
         </is>
       </c>
     </row>
@@ -2094,81 +2160,83 @@
           <t>Rennes</t>
         </is>
       </c>
-      <c r="D6" s="7" t="inlineStr">
+      <c r="D6" s="7" t="inlineStr"/>
+      <c r="E6" s="8" t="inlineStr">
         <is>
           <t>35</t>
         </is>
       </c>
-      <c r="E6" s="8" t="n">
+      <c r="F6" s="9" t="n">
         <v>56</v>
       </c>
-      <c r="F6" s="7" t="n">
+      <c r="G6" s="8" t="n">
         <v>6</v>
       </c>
-      <c r="G6" s="9" t="inlineStr">
-        <is>
-          <t>non</t>
-        </is>
-      </c>
-      <c r="H6" s="20" t="inlineStr">
+      <c r="H6" s="10" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="I6" s="22" t="inlineStr">
         <is>
           <t>oui</t>
         </is>
       </c>
-      <c r="I6" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="J6" s="11" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K6" s="12" t="inlineStr">
+        <is>
           <t>balises &lt;font&gt; (10) | non responsive | pas de @media | pas de flex/grid | pas de variables CSS | CSS tres court (434B) | aucun radius/ombre</t>
         </is>
       </c>
     </row>
     <row r="7" ht="30" customHeight="1">
-      <c r="A7" s="12" t="inlineStr">
+      <c r="A7" s="13" t="inlineStr">
         <is>
           <t>carrosserie-adamo.com</t>
         </is>
       </c>
-      <c r="B7" s="13" t="inlineStr">
+      <c r="B7" s="14" t="inlineStr">
         <is>
           <t>Carrosserie Adamo</t>
         </is>
       </c>
-      <c r="C7" s="14" t="inlineStr">
+      <c r="C7" s="15" t="inlineStr">
         <is>
           <t>Saint-Etienne</t>
         </is>
       </c>
-      <c r="D7" s="15" t="inlineStr">
+      <c r="D7" s="16" t="inlineStr"/>
+      <c r="E7" s="17" t="inlineStr">
         <is>
           <t>42</t>
         </is>
       </c>
-      <c r="E7" s="8" t="n">
+      <c r="F7" s="9" t="n">
         <v>56</v>
       </c>
-      <c r="F7" s="15" t="n">
+      <c r="G7" s="17" t="n">
         <v>6</v>
       </c>
-      <c r="G7" s="16" t="inlineStr">
-        <is>
-          <t>non</t>
-        </is>
-      </c>
-      <c r="H7" s="17" t="inlineStr">
+      <c r="H7" s="18" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="I7" s="19" t="inlineStr">
         <is>
           <t>oui</t>
         </is>
       </c>
-      <c r="I7" s="18" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J7" s="19" t="inlineStr">
+      <c r="J7" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K7" s="21" t="inlineStr">
         <is>
           <t>balises &lt;font&gt; (31) | non responsive | pas de @media | pas de flex/grid | pas de variables CSS | CSS tres court (434B) | aucun radius/ombre</t>
         </is>
@@ -2190,81 +2258,83 @@
           <t>Bayonne</t>
         </is>
       </c>
-      <c r="D8" s="7" t="inlineStr">
+      <c r="D8" s="7" t="inlineStr"/>
+      <c r="E8" s="8" t="inlineStr">
         <is>
           <t>64</t>
         </is>
       </c>
-      <c r="E8" s="8" t="n">
+      <c r="F8" s="9" t="n">
         <v>56</v>
       </c>
-      <c r="F8" s="7" t="n">
+      <c r="G8" s="8" t="n">
         <v>6</v>
       </c>
-      <c r="G8" s="9" t="inlineStr">
-        <is>
-          <t>non</t>
-        </is>
-      </c>
-      <c r="H8" s="20" t="inlineStr">
+      <c r="H8" s="10" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="I8" s="22" t="inlineStr">
         <is>
           <t>oui</t>
         </is>
       </c>
-      <c r="I8" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="J8" s="11" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K8" s="12" t="inlineStr">
+        <is>
           <t>balises &lt;font&gt; (5) | non responsive | pas de @media | pas de flex/grid | pas de variables CSS | CSS tres court (434B) | aucun radius/ombre</t>
         </is>
       </c>
     </row>
     <row r="9" ht="30" customHeight="1">
-      <c r="A9" s="12" t="inlineStr">
+      <c r="A9" s="13" t="inlineStr">
         <is>
           <t>carrosserievernoise.fr</t>
         </is>
       </c>
-      <c r="B9" s="13" t="inlineStr">
+      <c r="B9" s="14" t="inlineStr">
         <is>
           <t>Carrosserie Vernoise</t>
         </is>
       </c>
-      <c r="C9" s="14" t="inlineStr">
+      <c r="C9" s="15" t="inlineStr">
         <is>
           <t>Rennes</t>
         </is>
       </c>
-      <c r="D9" s="15" t="inlineStr">
+      <c r="D9" s="16" t="inlineStr"/>
+      <c r="E9" s="17" t="inlineStr">
         <is>
           <t>35</t>
         </is>
       </c>
-      <c r="E9" s="8" t="n">
+      <c r="F9" s="9" t="n">
         <v>56</v>
       </c>
-      <c r="F9" s="15" t="n">
+      <c r="G9" s="17" t="n">
         <v>6</v>
       </c>
-      <c r="G9" s="16" t="inlineStr">
-        <is>
-          <t>non</t>
-        </is>
-      </c>
-      <c r="H9" s="17" t="inlineStr">
+      <c r="H9" s="18" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="I9" s="19" t="inlineStr">
         <is>
           <t>oui</t>
         </is>
       </c>
-      <c r="I9" s="18" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J9" s="19" t="inlineStr">
+      <c r="J9" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K9" s="21" t="inlineStr">
         <is>
           <t>balises &lt;font&gt; (7) | non responsive | pas de @media | pas de flex/grid | pas de variables CSS | CSS tres court (434B) | aucun radius/ombre</t>
         </is>
@@ -2286,43 +2356,44 @@
           <t>La Rochelle</t>
         </is>
       </c>
-      <c r="D10" s="7" t="inlineStr">
+      <c r="D10" s="7" t="inlineStr"/>
+      <c r="E10" s="8" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="E10" s="8" t="n">
+      <c r="F10" s="9" t="n">
         <v>50</v>
       </c>
-      <c r="F10" s="7" t="n">
+      <c r="G10" s="8" t="n">
         <v>6</v>
       </c>
-      <c r="G10" s="9" t="inlineStr">
-        <is>
-          <t>non</t>
-        </is>
-      </c>
-      <c r="H10" s="20" t="inlineStr">
+      <c r="H10" s="10" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="I10" s="22" t="inlineStr">
         <is>
           <t>oui</t>
         </is>
       </c>
-      <c r="I10" s="10" t="inlineStr">
+      <c r="J10" s="11" t="inlineStr">
         <is>
           <t>lmsoft web creator pro, version:6.0.0.4</t>
         </is>
       </c>
-      <c r="J10" s="11" t="inlineStr">
+      <c r="K10" s="12" t="inlineStr">
         <is>
           <t>balises &lt;font&gt; (29) | non responsive | pas de @media | pas de flex/grid | pas de variables CSS | aucun radius/ombre</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:J10"/>
+  <autoFilter ref="A3:K10"/>
   <mergeCells count="2">
-    <mergeCell ref="A1:J1"/>
-    <mergeCell ref="A2:J2"/>
+    <mergeCell ref="A2:K2"/>
+    <mergeCell ref="A1:K1"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A4" r:id="rId1"/>
@@ -2343,19 +2414,20 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J10"/>
+  <dimension ref="A1:K10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
     <col width="26" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="6" customWidth="1" min="4" max="4"/>
-    <col width="9" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="4" max="4"/>
+    <col width="6" customWidth="1" min="5" max="5"/>
     <col width="9" customWidth="1" min="6" max="6"/>
-    <col width="11" customWidth="1" min="7" max="7"/>
-    <col width="8" customWidth="1" min="8" max="8"/>
-    <col width="20" customWidth="1" min="9" max="9"/>
-    <col width="62" customWidth="1" min="10" max="10"/>
+    <col width="9" customWidth="1" min="7" max="7"/>
+    <col width="11" customWidth="1" min="8" max="8"/>
+    <col width="8" customWidth="1" min="9" max="9"/>
+    <col width="20" customWidth="1" min="10" max="10"/>
+    <col width="62" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1" ht="34" customHeight="1">
@@ -2368,7 +2440,7 @@
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Classés du site le plus indéfendable au moins pire. « Laideur » = score de design daté ; « Ancien. » = signaux d'abandon.</t>
+          <t>Classés du site le plus indéfendable au moins pire. « Laideur » = score de design daté ; « Ancien. » = signaux d'abandon. « Zone » est le centre de recherche, pas l'adresse : la commune réelle n'est indiquée que lorsque le site l'affiche.</t>
         </is>
       </c>
     </row>
@@ -2385,40 +2457,45 @@
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>Ville</t>
+          <t>Zone de recherche</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
+          <t>Commune réelle</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
           <t>Dép.</t>
         </is>
       </c>
-      <c r="E3" s="3" t="inlineStr">
+      <c r="F3" s="3" t="inlineStr">
         <is>
           <t>Laideur</t>
         </is>
       </c>
-      <c r="F3" s="3" t="inlineStr">
+      <c r="G3" s="3" t="inlineStr">
         <is>
           <t>Ancien.</t>
         </is>
       </c>
-      <c r="G3" s="3" t="inlineStr">
+      <c r="H3" s="3" t="inlineStr">
         <is>
           <t>Responsive</t>
         </is>
       </c>
-      <c r="H3" s="3" t="inlineStr">
+      <c r="I3" s="3" t="inlineStr">
         <is>
           <t>HTTPS</t>
         </is>
       </c>
-      <c r="I3" s="3" t="inlineStr">
+      <c r="J3" s="3" t="inlineStr">
         <is>
           <t>Techno</t>
         </is>
       </c>
-      <c r="J3" s="3" t="inlineStr">
+      <c r="K3" s="3" t="inlineStr">
         <is>
           <t>Ce qui cloche</t>
         </is>
@@ -2440,81 +2517,83 @@
           <t>Paris</t>
         </is>
       </c>
-      <c r="D4" s="7" t="inlineStr">
+      <c r="D4" s="7" t="inlineStr"/>
+      <c r="E4" s="8" t="inlineStr">
         <is>
           <t>75</t>
         </is>
       </c>
-      <c r="E4" s="8" t="n">
+      <c r="F4" s="9" t="n">
         <v>60</v>
       </c>
-      <c r="F4" s="7" t="n">
+      <c r="G4" s="8" t="n">
         <v>6</v>
       </c>
-      <c r="G4" s="9" t="inlineStr">
-        <is>
-          <t>non</t>
-        </is>
-      </c>
-      <c r="H4" s="20" t="inlineStr">
+      <c r="H4" s="10" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="I4" s="22" t="inlineStr">
         <is>
           <t>oui</t>
         </is>
       </c>
-      <c r="I4" s="10" t="inlineStr">
+      <c r="J4" s="11" t="inlineStr">
         <is>
           <t>bueno 1.5.1</t>
         </is>
       </c>
-      <c r="J4" s="11" t="inlineStr">
+      <c r="K4" s="12" t="inlineStr">
         <is>
           <t>&lt;center&gt; | bgcolor= | doctype ancien | non responsive | pas de @media | pas de flex/grid | pas de variables CSS | CSS tres court (2B) | aucun radius/ombre</t>
         </is>
       </c>
     </row>
     <row r="5" ht="30" customHeight="1">
-      <c r="A5" s="12" t="inlineStr">
+      <c r="A5" s="13" t="inlineStr">
         <is>
           <t>cyclolivine.fr</t>
         </is>
       </c>
-      <c r="B5" s="13" t="inlineStr">
+      <c r="B5" s="14" t="inlineStr">
         <is>
           <t>Cyclolivine</t>
         </is>
       </c>
-      <c r="C5" s="14" t="inlineStr">
+      <c r="C5" s="15" t="inlineStr">
         <is>
           <t>Grenoble</t>
         </is>
       </c>
-      <c r="D5" s="15" t="inlineStr">
+      <c r="D5" s="16" t="inlineStr"/>
+      <c r="E5" s="17" t="inlineStr">
         <is>
           <t>38</t>
         </is>
       </c>
-      <c r="E5" s="21" t="n">
+      <c r="F5" s="23" t="n">
         <v>49</v>
       </c>
-      <c r="F5" s="15" t="n">
+      <c r="G5" s="17" t="n">
         <v>8</v>
       </c>
-      <c r="G5" s="16" t="inlineStr">
-        <is>
-          <t>non</t>
-        </is>
-      </c>
-      <c r="H5" s="16" t="inlineStr">
+      <c r="H5" s="18" t="inlineStr">
         <is>
           <t>non</t>
         </is>
       </c>
       <c r="I5" s="18" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J5" s="19" t="inlineStr">
+          <t>non</t>
+        </is>
+      </c>
+      <c r="J5" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K5" s="21" t="inlineStr">
         <is>
           <t>&lt;center&gt; | doctype ancien | non responsive | pas de @media | pas de flex/grid | pas de variables CSS | aucun radius/ombre</t>
         </is>
@@ -2536,81 +2615,83 @@
           <t>Rennes</t>
         </is>
       </c>
-      <c r="D6" s="7" t="inlineStr">
+      <c r="D6" s="7" t="inlineStr"/>
+      <c r="E6" s="8" t="inlineStr">
         <is>
           <t>35</t>
         </is>
       </c>
-      <c r="E6" s="21" t="n">
+      <c r="F6" s="23" t="n">
         <v>49</v>
       </c>
-      <c r="F6" s="7" t="n">
+      <c r="G6" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="G6" s="20" t="inlineStr">
+      <c r="H6" s="22" t="inlineStr">
         <is>
           <t>oui</t>
         </is>
       </c>
-      <c r="H6" s="20" t="inlineStr">
+      <c r="I6" s="22" t="inlineStr">
         <is>
           <t>oui</t>
         </is>
       </c>
-      <c r="I6" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="J6" s="11" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K6" s="12" t="inlineStr">
+        <is>
           <t>layout en tableaux (4) | balises &lt;font&gt; (29) | pas de @media | pas de flex/grid | pas de variables CSS | aucun radius/ombre</t>
         </is>
       </c>
     </row>
     <row r="7" ht="30" customHeight="1">
-      <c r="A7" s="12" t="inlineStr">
+      <c r="A7" s="13" t="inlineStr">
         <is>
           <t>velosapiens.fr</t>
         </is>
       </c>
-      <c r="B7" s="13" t="inlineStr">
+      <c r="B7" s="14" t="inlineStr">
         <is>
           <t>Vélo-Sapiens</t>
         </is>
       </c>
-      <c r="C7" s="14" t="inlineStr">
+      <c r="C7" s="15" t="inlineStr">
         <is>
           <t>Marseille</t>
         </is>
       </c>
-      <c r="D7" s="15" t="inlineStr">
+      <c r="D7" s="16" t="inlineStr"/>
+      <c r="E7" s="17" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="E7" s="21" t="n">
+      <c r="F7" s="23" t="n">
         <v>45</v>
       </c>
-      <c r="F7" s="15" t="n">
+      <c r="G7" s="17" t="n">
         <v>6</v>
       </c>
-      <c r="G7" s="16" t="inlineStr">
-        <is>
-          <t>non</t>
-        </is>
-      </c>
-      <c r="H7" s="17" t="inlineStr">
+      <c r="H7" s="18" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="I7" s="19" t="inlineStr">
         <is>
           <t>oui</t>
         </is>
       </c>
-      <c r="I7" s="18" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J7" s="19" t="inlineStr">
+      <c r="J7" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K7" s="21" t="inlineStr">
         <is>
           <t>&lt;center&gt; | non responsive | pas de @media | pas de flex/grid | pas de variables CSS | aucun radius/ombre</t>
         </is>
@@ -2622,87 +2703,97 @@
           <t>laveriedebretagne.free.fr</t>
         </is>
       </c>
-      <c r="B8" s="5" t="inlineStr"/>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>Laverie de Montigny-le-Bretonneux</t>
+        </is>
+      </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
           <t>Paris</t>
         </is>
       </c>
-      <c r="D8" s="7" t="inlineStr">
+      <c r="D8" s="24" t="inlineStr">
+        <is>
+          <t>Montigny-le-Bretonneux (78180)</t>
+        </is>
+      </c>
+      <c r="E8" s="8" t="inlineStr">
         <is>
           <t>75</t>
         </is>
       </c>
-      <c r="E8" s="21" t="n">
+      <c r="F8" s="23" t="n">
         <v>43</v>
       </c>
-      <c r="F8" s="7" t="n">
+      <c r="G8" s="8" t="n">
         <v>8</v>
       </c>
-      <c r="G8" s="9" t="inlineStr">
-        <is>
-          <t>non</t>
-        </is>
-      </c>
-      <c r="H8" s="9" t="inlineStr">
+      <c r="H8" s="10" t="inlineStr">
         <is>
           <t>non</t>
         </is>
       </c>
       <c r="I8" s="10" t="inlineStr">
         <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="J8" s="11" t="inlineStr">
+        <is>
           <t>izispot 4.31 (www.izispot.com)</t>
         </is>
       </c>
-      <c r="J8" s="11" t="inlineStr">
+      <c r="K8" s="12" t="inlineStr">
         <is>
           <t>layout en tableaux (5) | balises &lt;font&gt; (4) | doctype ancien | non responsive</t>
         </is>
       </c>
     </row>
     <row r="9" ht="30" customHeight="1">
-      <c r="A9" s="12" t="inlineStr">
+      <c r="A9" s="13" t="inlineStr">
         <is>
           <t>jpcycles.sitego.fr</t>
         </is>
       </c>
-      <c r="B9" s="13" t="inlineStr">
+      <c r="B9" s="14" t="inlineStr">
         <is>
           <t>JP Cycles</t>
         </is>
       </c>
-      <c r="C9" s="14" t="inlineStr">
+      <c r="C9" s="15" t="inlineStr">
         <is>
           <t>Paris</t>
         </is>
       </c>
-      <c r="D9" s="15" t="inlineStr">
+      <c r="D9" s="16" t="inlineStr"/>
+      <c r="E9" s="17" t="inlineStr">
         <is>
           <t>75</t>
         </is>
       </c>
-      <c r="E9" s="21" t="n">
+      <c r="F9" s="23" t="n">
         <v>37</v>
       </c>
-      <c r="F9" s="15" t="n">
+      <c r="G9" s="17" t="n">
         <v>3</v>
       </c>
-      <c r="G9" s="16" t="inlineStr">
-        <is>
-          <t>non</t>
-        </is>
-      </c>
-      <c r="H9" s="17" t="inlineStr">
+      <c r="H9" s="18" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="I9" s="19" t="inlineStr">
         <is>
           <t>oui</t>
         </is>
       </c>
-      <c r="I9" s="18" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J9" s="19" t="inlineStr">
+      <c r="J9" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K9" s="21" t="inlineStr">
         <is>
           <t>non responsive | pas de @media | pas de flex/grid | pas de variables CSS</t>
         </is>
@@ -2724,43 +2815,44 @@
           <t>Paris</t>
         </is>
       </c>
-      <c r="D10" s="7" t="inlineStr">
+      <c r="D10" s="7" t="inlineStr"/>
+      <c r="E10" s="8" t="inlineStr">
         <is>
           <t>75</t>
         </is>
       </c>
-      <c r="E10" s="21" t="n">
+      <c r="F10" s="23" t="n">
         <v>36</v>
       </c>
-      <c r="F10" s="7" t="n">
+      <c r="G10" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="G10" s="20" t="inlineStr">
+      <c r="H10" s="22" t="inlineStr">
         <is>
           <t>oui</t>
         </is>
       </c>
-      <c r="H10" s="20" t="inlineStr">
+      <c r="I10" s="22" t="inlineStr">
         <is>
           <t>oui</t>
         </is>
       </c>
-      <c r="I10" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="J10" s="11" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K10" s="12" t="inlineStr">
+        <is>
           <t>layout en tableaux (3) | pas de @media | pas de flex/grid | aucun radius/ombre</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:J10"/>
+  <autoFilter ref="A3:K10"/>
   <mergeCells count="2">
-    <mergeCell ref="A1:J1"/>
-    <mergeCell ref="A2:J2"/>
+    <mergeCell ref="A2:K2"/>
+    <mergeCell ref="A1:K1"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A4" r:id="rId1"/>

--- a/lot_01.xlsx
+++ b/lot_01.xlsx
@@ -153,7 +153,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -223,6 +223,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1590,39 +1593,43 @@
     <row r="4" ht="30" customHeight="1">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>babacanteen.com</t>
+          <t>resto.krutenau.free.fr</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>Baba canteen</t>
+          <t>Winstub La Krutenau</t>
         </is>
       </c>
       <c r="C4" s="6" t="inlineStr">
         <is>
-          <t>Toulouse</t>
-        </is>
-      </c>
-      <c r="D4" s="7" t="inlineStr"/>
+          <t>Colmar</t>
+        </is>
+      </c>
+      <c r="D4" s="24" t="inlineStr">
+        <is>
+          <t>Colmar (68000)</t>
+        </is>
+      </c>
       <c r="E4" s="8" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>68</t>
         </is>
       </c>
       <c r="F4" s="9" t="n">
-        <v>60</v>
+        <v>79</v>
       </c>
       <c r="G4" s="8" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="H4" s="10" t="inlineStr">
         <is>
           <t>non</t>
         </is>
       </c>
-      <c r="I4" s="22" t="inlineStr">
-        <is>
-          <t>oui</t>
+      <c r="I4" s="10" t="inlineStr">
+        <is>
+          <t>non</t>
         </is>
       </c>
       <c r="J4" s="11" t="inlineStr">
@@ -1632,46 +1639,46 @@
       </c>
       <c r="K4" s="12" t="inlineStr">
         <is>
-          <t>balises &lt;font&gt; (5) | non responsive | document.write | pas de @media | pas de flex/grid | pas de variables CSS | CSS tres court (3B) | aucun radius/ombre</t>
+          <t>layout en tableaux (23) | &lt;marquee&gt; | bgcolor= | doctype ancien | non responsive | images .gif | pas de @media | px uniquement | pas de flex/grid | pas de variables CSS | aucun radius/ombre</t>
         </is>
       </c>
     </row>
     <row r="5" ht="30" customHeight="1">
       <c r="A5" s="13" t="inlineStr">
         <is>
-          <t>chezmario.fr</t>
+          <t>babacanteen.com</t>
         </is>
       </c>
       <c r="B5" s="14" t="inlineStr">
         <is>
-          <t>Chez Mario</t>
+          <t>Baba canteen</t>
         </is>
       </c>
       <c r="C5" s="15" t="inlineStr">
         <is>
-          <t>Bordeaux</t>
+          <t>Toulouse</t>
         </is>
       </c>
       <c r="D5" s="16" t="inlineStr"/>
       <c r="E5" s="17" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>31</t>
         </is>
       </c>
       <c r="F5" s="9" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="G5" s="17" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H5" s="18" t="inlineStr">
         <is>
           <t>non</t>
         </is>
       </c>
-      <c r="I5" s="18" t="inlineStr">
-        <is>
-          <t>non</t>
+      <c r="I5" s="19" t="inlineStr">
+        <is>
+          <t>oui</t>
         </is>
       </c>
       <c r="J5" s="20" t="inlineStr">
@@ -1681,46 +1688,46 @@
       </c>
       <c r="K5" s="21" t="inlineStr">
         <is>
-          <t>layout en tableaux (4) | doctype ancien | non responsive | pas de @media | pas de flex/grid | pas de variables CSS | aucun radius/ombre</t>
+          <t>balises &lt;font&gt; (5) | non responsive | document.write | pas de @media | pas de flex/grid | pas de variables CSS | CSS tres court (3B) | aucun radius/ombre</t>
         </is>
       </c>
     </row>
     <row r="6" ht="30" customHeight="1">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>baan.fr</t>
+          <t>chezmario.fr</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>Baan Siam</t>
+          <t>Chez Mario</t>
         </is>
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>Toulouse</t>
+          <t>Bordeaux</t>
         </is>
       </c>
       <c r="D6" s="7" t="inlineStr"/>
       <c r="E6" s="8" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>33</t>
         </is>
       </c>
       <c r="F6" s="9" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G6" s="8" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H6" s="10" t="inlineStr">
         <is>
           <t>non</t>
         </is>
       </c>
-      <c r="I6" s="22" t="inlineStr">
-        <is>
-          <t>oui</t>
+      <c r="I6" s="10" t="inlineStr">
+        <is>
+          <t>non</t>
         </is>
       </c>
       <c r="J6" s="11" t="inlineStr">
@@ -1730,46 +1737,46 @@
       </c>
       <c r="K6" s="12" t="inlineStr">
         <is>
-          <t>layout en tableaux (9) | balises &lt;font&gt; (32) | &lt;center&gt; | bgcolor= | sans doctype | non responsive | images .gif</t>
+          <t>layout en tableaux (4) | doctype ancien | non responsive | pas de @media | pas de flex/grid | pas de variables CSS | aucun radius/ombre</t>
         </is>
       </c>
     </row>
     <row r="7" ht="30" customHeight="1">
       <c r="A7" s="13" t="inlineStr">
         <is>
-          <t>lechateausormiou.fr</t>
+          <t>baan.fr</t>
         </is>
       </c>
       <c r="B7" s="14" t="inlineStr">
         <is>
-          <t>Le Château Sormiou</t>
+          <t>Baan Siam</t>
         </is>
       </c>
       <c r="C7" s="15" t="inlineStr">
         <is>
-          <t>Marseille</t>
+          <t>Toulouse</t>
         </is>
       </c>
       <c r="D7" s="16" t="inlineStr"/>
       <c r="E7" s="17" t="inlineStr">
         <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="F7" s="23" t="n">
-        <v>47</v>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="F7" s="9" t="n">
+        <v>57</v>
       </c>
       <c r="G7" s="17" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="H7" s="18" t="inlineStr">
         <is>
           <t>non</t>
         </is>
       </c>
-      <c r="I7" s="18" t="inlineStr">
-        <is>
-          <t>non</t>
+      <c r="I7" s="19" t="inlineStr">
+        <is>
+          <t>oui</t>
         </is>
       </c>
       <c r="J7" s="20" t="inlineStr">
@@ -1779,50 +1786,46 @@
       </c>
       <c r="K7" s="21" t="inlineStr">
         <is>
-          <t>balises &lt;font&gt; (1) | non responsive | pas de @media | pas de flex/grid | pas de variables CSS</t>
+          <t>layout en tableaux (9) | balises &lt;font&gt; (32) | &lt;center&gt; | bgcolor= | sans doctype | non responsive | images .gif</t>
         </is>
       </c>
     </row>
     <row r="8" ht="30" customHeight="1">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>ldvdraveil.fr</t>
+          <t>lechateausormiou.fr</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>La Dolce Vita</t>
+          <t>Le Château Sormiou</t>
         </is>
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>Paris</t>
-        </is>
-      </c>
-      <c r="D8" s="24" t="inlineStr">
-        <is>
-          <t>Draveil (91210)</t>
-        </is>
-      </c>
+          <t>Marseille</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr"/>
       <c r="E8" s="8" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>13</t>
         </is>
       </c>
       <c r="F8" s="23" t="n">
         <v>47</v>
       </c>
       <c r="G8" s="8" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="H8" s="10" t="inlineStr">
         <is>
           <t>non</t>
         </is>
       </c>
-      <c r="I8" s="22" t="inlineStr">
-        <is>
-          <t>oui</t>
+      <c r="I8" s="10" t="inlineStr">
+        <is>
+          <t>non</t>
         </is>
       </c>
       <c r="J8" s="11" t="inlineStr">
@@ -1832,7 +1835,7 @@
       </c>
       <c r="K8" s="12" t="inlineStr">
         <is>
-          <t>layout en tableaux (29) | balises &lt;font&gt; (4) | &lt;center&gt; | non responsive | &lt;br&gt; en masse</t>
+          <t>balises &lt;font&gt; (1) | non responsive | pas de @media | pas de flex/grid | pas de variables CSS</t>
         </is>
       </c>
     </row>
@@ -2553,39 +2556,43 @@
     <row r="5" ht="30" customHeight="1">
       <c r="A5" s="13" t="inlineStr">
         <is>
-          <t>cyclolivine.fr</t>
+          <t>atelierdumenager.com</t>
         </is>
       </c>
       <c r="B5" s="14" t="inlineStr">
         <is>
-          <t>Cyclolivine</t>
+          <t>Atelier du ménager</t>
         </is>
       </c>
       <c r="C5" s="15" t="inlineStr">
         <is>
-          <t>Grenoble</t>
-        </is>
-      </c>
-      <c r="D5" s="16" t="inlineStr"/>
+          <t>Poitiers</t>
+        </is>
+      </c>
+      <c r="D5" s="25" t="inlineStr">
+        <is>
+          <t>Poitiers (86000)</t>
+        </is>
+      </c>
       <c r="E5" s="17" t="inlineStr">
         <is>
-          <t>38</t>
-        </is>
-      </c>
-      <c r="F5" s="23" t="n">
-        <v>49</v>
+          <t>86</t>
+        </is>
+      </c>
+      <c r="F5" s="9" t="n">
+        <v>56</v>
       </c>
       <c r="G5" s="17" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="H5" s="18" t="inlineStr">
         <is>
           <t>non</t>
         </is>
       </c>
-      <c r="I5" s="18" t="inlineStr">
-        <is>
-          <t>non</t>
+      <c r="I5" s="19" t="inlineStr">
+        <is>
+          <t>oui</t>
         </is>
       </c>
       <c r="J5" s="20" t="inlineStr">
@@ -2595,46 +2602,46 @@
       </c>
       <c r="K5" s="21" t="inlineStr">
         <is>
-          <t>&lt;center&gt; | doctype ancien | non responsive | pas de @media | pas de flex/grid | pas de variables CSS | aucun radius/ombre</t>
+          <t>balises &lt;font&gt; (2) | non responsive | pas de @media | pas de flex/grid | pas de variables CSS | CSS tres court (434B) | aucun radius/ombre</t>
         </is>
       </c>
     </row>
     <row r="6" ht="30" customHeight="1">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>rustine-beaulieu.weebly.com</t>
+          <t>cyclolivine.fr</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>La Rustine de Beaulieu</t>
+          <t>Cyclolivine</t>
         </is>
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>Rennes</t>
+          <t>Grenoble</t>
         </is>
       </c>
       <c r="D6" s="7" t="inlineStr"/>
       <c r="E6" s="8" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>38</t>
         </is>
       </c>
       <c r="F6" s="23" t="n">
         <v>49</v>
       </c>
       <c r="G6" s="8" t="n">
-        <v>3</v>
-      </c>
-      <c r="H6" s="22" t="inlineStr">
-        <is>
-          <t>oui</t>
-        </is>
-      </c>
-      <c r="I6" s="22" t="inlineStr">
-        <is>
-          <t>oui</t>
+        <v>8</v>
+      </c>
+      <c r="H6" s="10" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="I6" s="10" t="inlineStr">
+        <is>
+          <t>non</t>
         </is>
       </c>
       <c r="J6" s="11" t="inlineStr">
@@ -2644,41 +2651,41 @@
       </c>
       <c r="K6" s="12" t="inlineStr">
         <is>
-          <t>layout en tableaux (4) | balises &lt;font&gt; (29) | pas de @media | pas de flex/grid | pas de variables CSS | aucun radius/ombre</t>
+          <t>&lt;center&gt; | doctype ancien | non responsive | pas de @media | pas de flex/grid | pas de variables CSS | aucun radius/ombre</t>
         </is>
       </c>
     </row>
     <row r="7" ht="30" customHeight="1">
       <c r="A7" s="13" t="inlineStr">
         <is>
-          <t>velosapiens.fr</t>
+          <t>rustine-beaulieu.weebly.com</t>
         </is>
       </c>
       <c r="B7" s="14" t="inlineStr">
         <is>
-          <t>Vélo-Sapiens</t>
+          <t>La Rustine de Beaulieu</t>
         </is>
       </c>
       <c r="C7" s="15" t="inlineStr">
         <is>
-          <t>Marseille</t>
+          <t>Rennes</t>
         </is>
       </c>
       <c r="D7" s="16" t="inlineStr"/>
       <c r="E7" s="17" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>35</t>
         </is>
       </c>
       <c r="F7" s="23" t="n">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="G7" s="17" t="n">
-        <v>6</v>
-      </c>
-      <c r="H7" s="18" t="inlineStr">
-        <is>
-          <t>non</t>
+        <v>3</v>
+      </c>
+      <c r="H7" s="19" t="inlineStr">
+        <is>
+          <t>oui</t>
         </is>
       </c>
       <c r="I7" s="19" t="inlineStr">
@@ -2693,60 +2700,56 @@
       </c>
       <c r="K7" s="21" t="inlineStr">
         <is>
-          <t>&lt;center&gt; | non responsive | pas de @media | pas de flex/grid | pas de variables CSS | aucun radius/ombre</t>
+          <t>layout en tableaux (4) | balises &lt;font&gt; (29) | pas de @media | pas de flex/grid | pas de variables CSS | aucun radius/ombre</t>
         </is>
       </c>
     </row>
     <row r="8" ht="30" customHeight="1">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>laveriedebretagne.free.fr</t>
+          <t>velosapiens.fr</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>Laverie de Montigny-le-Bretonneux</t>
+          <t>Vélo-Sapiens</t>
         </is>
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>Paris</t>
-        </is>
-      </c>
-      <c r="D8" s="24" t="inlineStr">
-        <is>
-          <t>Montigny-le-Bretonneux (78180)</t>
-        </is>
-      </c>
+          <t>Marseille</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr"/>
       <c r="E8" s="8" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>13</t>
         </is>
       </c>
       <c r="F8" s="23" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="G8" s="8" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="H8" s="10" t="inlineStr">
         <is>
           <t>non</t>
         </is>
       </c>
-      <c r="I8" s="10" t="inlineStr">
-        <is>
-          <t>non</t>
+      <c r="I8" s="22" t="inlineStr">
+        <is>
+          <t>oui</t>
         </is>
       </c>
       <c r="J8" s="11" t="inlineStr">
         <is>
-          <t>izispot 4.31 (www.izispot.com)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="K8" s="12" t="inlineStr">
         <is>
-          <t>layout en tableaux (5) | balises &lt;font&gt; (4) | doctype ancien | non responsive</t>
+          <t>&lt;center&gt; | non responsive | pas de @media | pas de flex/grid | pas de variables CSS | aucun radius/ombre</t>
         </is>
       </c>
     </row>

--- a/lot_01.xlsx
+++ b/lot_01.xlsx
@@ -1593,43 +1593,39 @@
     <row r="4" ht="30" customHeight="1">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>resto.krutenau.free.fr</t>
+          <t>babacanteen.com</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>Winstub La Krutenau</t>
+          <t>Baba canteen</t>
         </is>
       </c>
       <c r="C4" s="6" t="inlineStr">
         <is>
-          <t>Colmar</t>
-        </is>
-      </c>
-      <c r="D4" s="24" t="inlineStr">
-        <is>
-          <t>Colmar (68000)</t>
-        </is>
-      </c>
+          <t>Toulouse</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr"/>
       <c r="E4" s="8" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>31</t>
         </is>
       </c>
       <c r="F4" s="9" t="n">
-        <v>79</v>
+        <v>60</v>
       </c>
       <c r="G4" s="8" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="H4" s="10" t="inlineStr">
         <is>
           <t>non</t>
         </is>
       </c>
-      <c r="I4" s="10" t="inlineStr">
-        <is>
-          <t>non</t>
+      <c r="I4" s="22" t="inlineStr">
+        <is>
+          <t>oui</t>
         </is>
       </c>
       <c r="J4" s="11" t="inlineStr">
@@ -1639,46 +1635,46 @@
       </c>
       <c r="K4" s="12" t="inlineStr">
         <is>
-          <t>layout en tableaux (23) | &lt;marquee&gt; | bgcolor= | doctype ancien | non responsive | images .gif | pas de @media | px uniquement | pas de flex/grid | pas de variables CSS | aucun radius/ombre</t>
+          <t>balises &lt;font&gt; (5) | non responsive | document.write | pas de @media | pas de flex/grid | pas de variables CSS | CSS tres court (3B) | aucun radius/ombre</t>
         </is>
       </c>
     </row>
     <row r="5" ht="30" customHeight="1">
       <c r="A5" s="13" t="inlineStr">
         <is>
-          <t>babacanteen.com</t>
+          <t>chezmario.fr</t>
         </is>
       </c>
       <c r="B5" s="14" t="inlineStr">
         <is>
-          <t>Baba canteen</t>
+          <t>Chez Mario</t>
         </is>
       </c>
       <c r="C5" s="15" t="inlineStr">
         <is>
-          <t>Toulouse</t>
+          <t>Bordeaux</t>
         </is>
       </c>
       <c r="D5" s="16" t="inlineStr"/>
       <c r="E5" s="17" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>33</t>
         </is>
       </c>
       <c r="F5" s="9" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="G5" s="17" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H5" s="18" t="inlineStr">
         <is>
           <t>non</t>
         </is>
       </c>
-      <c r="I5" s="19" t="inlineStr">
-        <is>
-          <t>oui</t>
+      <c r="I5" s="18" t="inlineStr">
+        <is>
+          <t>non</t>
         </is>
       </c>
       <c r="J5" s="20" t="inlineStr">
@@ -1688,46 +1684,46 @@
       </c>
       <c r="K5" s="21" t="inlineStr">
         <is>
-          <t>balises &lt;font&gt; (5) | non responsive | document.write | pas de @media | pas de flex/grid | pas de variables CSS | CSS tres court (3B) | aucun radius/ombre</t>
+          <t>layout en tableaux (4) | doctype ancien | non responsive | pas de @media | pas de flex/grid | pas de variables CSS | aucun radius/ombre</t>
         </is>
       </c>
     </row>
     <row r="6" ht="30" customHeight="1">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>chezmario.fr</t>
+          <t>baan.fr</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>Chez Mario</t>
+          <t>Baan Siam</t>
         </is>
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>Bordeaux</t>
+          <t>Toulouse</t>
         </is>
       </c>
       <c r="D6" s="7" t="inlineStr"/>
       <c r="E6" s="8" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>31</t>
         </is>
       </c>
       <c r="F6" s="9" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G6" s="8" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H6" s="10" t="inlineStr">
         <is>
           <t>non</t>
         </is>
       </c>
-      <c r="I6" s="10" t="inlineStr">
-        <is>
-          <t>non</t>
+      <c r="I6" s="22" t="inlineStr">
+        <is>
+          <t>oui</t>
         </is>
       </c>
       <c r="J6" s="11" t="inlineStr">
@@ -1737,46 +1733,46 @@
       </c>
       <c r="K6" s="12" t="inlineStr">
         <is>
-          <t>layout en tableaux (4) | doctype ancien | non responsive | pas de @media | pas de flex/grid | pas de variables CSS | aucun radius/ombre</t>
+          <t>layout en tableaux (9) | balises &lt;font&gt; (32) | &lt;center&gt; | bgcolor= | sans doctype | non responsive | images .gif</t>
         </is>
       </c>
     </row>
     <row r="7" ht="30" customHeight="1">
       <c r="A7" s="13" t="inlineStr">
         <is>
-          <t>baan.fr</t>
+          <t>lechateausormiou.fr</t>
         </is>
       </c>
       <c r="B7" s="14" t="inlineStr">
         <is>
-          <t>Baan Siam</t>
+          <t>Le Château Sormiou</t>
         </is>
       </c>
       <c r="C7" s="15" t="inlineStr">
         <is>
-          <t>Toulouse</t>
+          <t>Marseille</t>
         </is>
       </c>
       <c r="D7" s="16" t="inlineStr"/>
       <c r="E7" s="17" t="inlineStr">
         <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="F7" s="9" t="n">
-        <v>57</v>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="F7" s="23" t="n">
+        <v>47</v>
       </c>
       <c r="G7" s="17" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="H7" s="18" t="inlineStr">
         <is>
           <t>non</t>
         </is>
       </c>
-      <c r="I7" s="19" t="inlineStr">
-        <is>
-          <t>oui</t>
+      <c r="I7" s="18" t="inlineStr">
+        <is>
+          <t>non</t>
         </is>
       </c>
       <c r="J7" s="20" t="inlineStr">
@@ -1786,46 +1782,50 @@
       </c>
       <c r="K7" s="21" t="inlineStr">
         <is>
-          <t>layout en tableaux (9) | balises &lt;font&gt; (32) | &lt;center&gt; | bgcolor= | sans doctype | non responsive | images .gif</t>
+          <t>balises &lt;font&gt; (1) | non responsive | pas de @media | pas de flex/grid | pas de variables CSS</t>
         </is>
       </c>
     </row>
     <row r="8" ht="30" customHeight="1">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>lechateausormiou.fr</t>
+          <t>ldvdraveil.fr</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>Le Château Sormiou</t>
+          <t>La Dolce Vita</t>
         </is>
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>Marseille</t>
-        </is>
-      </c>
-      <c r="D8" s="7" t="inlineStr"/>
+          <t>Paris</t>
+        </is>
+      </c>
+      <c r="D8" s="24" t="inlineStr">
+        <is>
+          <t>Draveil (91210)</t>
+        </is>
+      </c>
       <c r="E8" s="8" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>75</t>
         </is>
       </c>
       <c r="F8" s="23" t="n">
         <v>47</v>
       </c>
       <c r="G8" s="8" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="H8" s="10" t="inlineStr">
         <is>
           <t>non</t>
         </is>
       </c>
-      <c r="I8" s="10" t="inlineStr">
-        <is>
-          <t>non</t>
+      <c r="I8" s="22" t="inlineStr">
+        <is>
+          <t>oui</t>
         </is>
       </c>
       <c r="J8" s="11" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="K8" s="12" t="inlineStr">
         <is>
-          <t>balises &lt;font&gt; (1) | non responsive | pas de @media | pas de flex/grid | pas de variables CSS</t>
+          <t>layout en tableaux (29) | balises &lt;font&gt; (4) | &lt;center&gt; | non responsive | &lt;br&gt; en masse</t>
         </is>
       </c>
     </row>

--- a/lot_01.xlsx
+++ b/lot_01.xlsx
@@ -27,7 +27,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="12">
+  <fonts count="11">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -78,25 +78,19 @@
     </font>
     <font>
       <name val="Calibri"/>
-      <color rgb="006B7280"/>
-      <sz val="9"/>
+      <color rgb="00047857"/>
+      <sz val="10"/>
     </font>
     <font>
       <name val="Calibri"/>
-      <color rgb="00047857"/>
-      <sz val="10"/>
+      <color rgb="006B7280"/>
+      <sz val="9"/>
     </font>
     <font>
       <name val="Calibri"/>
       <b val="1"/>
       <color rgb="0092400E"/>
       <sz val="11"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <b val="1"/>
-      <color rgb="00111827"/>
-      <sz val="10"/>
     </font>
   </fonts>
   <fills count="6">
@@ -153,7 +147,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -168,7 +162,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -184,9 +178,12 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -195,7 +192,7 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -207,26 +204,17 @@
     <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -683,12 +671,12 @@
     <row r="4" ht="30" customHeight="1">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>multitude-lyon.fr</t>
+          <t>petezki.fr</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>Multitude</t>
+          <t>Petezki &amp; Fils</t>
         </is>
       </c>
       <c r="C4" s="6" t="inlineStr">
@@ -703,199 +691,199 @@
         </is>
       </c>
       <c r="F4" s="9" t="n">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="G4" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="H4" s="10" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="I4" s="11" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="J4" s="12" t="inlineStr">
+        <is>
+          <t>macromedia dreamweaver 8</t>
+        </is>
+      </c>
+      <c r="K4" s="13" t="inlineStr">
+        <is>
+          <t>layout en tableaux (9) | doctype ancien | non responsive | images .gif | pas de @media | px uniquement | pas de flex/grid | pas de variables CSS | aucun radius/ombre</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="30" customHeight="1">
+      <c r="A5" s="14" t="inlineStr">
+        <is>
+          <t>ardoise-zinc.fr</t>
+        </is>
+      </c>
+      <c r="B5" s="15" t="inlineStr">
+        <is>
+          <t>Ardoise et Zinc</t>
+        </is>
+      </c>
+      <c r="C5" s="16" t="inlineStr">
+        <is>
+          <t>Rennes</t>
+        </is>
+      </c>
+      <c r="D5" s="17" t="inlineStr"/>
+      <c r="E5" s="18" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="F5" s="9" t="n">
+        <v>56</v>
+      </c>
+      <c r="G5" s="18" t="n">
         <v>8</v>
       </c>
-      <c r="H4" s="10" t="inlineStr">
-        <is>
-          <t>non</t>
-        </is>
-      </c>
-      <c r="I4" s="10" t="inlineStr">
-        <is>
-          <t>non</t>
-        </is>
-      </c>
-      <c r="J4" s="11" t="inlineStr">
+      <c r="H5" s="19" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="I5" s="20" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="J5" s="21" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="K4" s="12" t="inlineStr">
-        <is>
-          <t>layout en tableaux (5) | balises &lt;font&gt; (1) | doctype ancien | non responsive | pas de @media | px uniquement | pas de flex/grid | pas de variables CSS | aucun radius/ombre</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="30" customHeight="1">
-      <c r="A5" s="13" t="inlineStr">
-        <is>
-          <t>petezki.fr</t>
-        </is>
-      </c>
-      <c r="B5" s="14" t="inlineStr">
-        <is>
-          <t>Petezki &amp; Fils</t>
-        </is>
-      </c>
-      <c r="C5" s="15" t="inlineStr">
-        <is>
-          <t>Lyon</t>
-        </is>
-      </c>
-      <c r="D5" s="16" t="inlineStr"/>
-      <c r="E5" s="17" t="inlineStr">
-        <is>
-          <t>69</t>
-        </is>
-      </c>
-      <c r="F5" s="9" t="n">
-        <v>67</v>
-      </c>
-      <c r="G5" s="17" t="n">
-        <v>6</v>
-      </c>
-      <c r="H5" s="18" t="inlineStr">
-        <is>
-          <t>non</t>
-        </is>
-      </c>
-      <c r="I5" s="19" t="inlineStr">
-        <is>
-          <t>oui</t>
-        </is>
-      </c>
-      <c r="J5" s="20" t="inlineStr">
-        <is>
-          <t>macromedia dreamweaver 8</t>
-        </is>
-      </c>
-      <c r="K5" s="21" t="inlineStr">
-        <is>
-          <t>layout en tableaux (9) | doctype ancien | non responsive | images .gif | pas de @media | px uniquement | pas de flex/grid | pas de variables CSS | aucun radius/ombre</t>
+      <c r="K5" s="22" t="inlineStr">
+        <is>
+          <t>balises &lt;font&gt; (13) | non responsive | pas de @media | pas de flex/grid | pas de variables CSS | CSS tres court (434B) | aucun radius/ombre</t>
         </is>
       </c>
     </row>
     <row r="6" ht="30" customHeight="1">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>ardoise-zinc.fr</t>
+          <t>atie-bat.fr</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>Ardoise et Zinc</t>
+          <t>Atie Bat</t>
         </is>
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>Rennes</t>
+          <t>Paris</t>
         </is>
       </c>
       <c r="D6" s="7" t="inlineStr"/>
       <c r="E6" s="8" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>75</t>
         </is>
       </c>
       <c r="F6" s="9" t="n">
         <v>56</v>
       </c>
       <c r="G6" s="8" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="H6" s="10" t="inlineStr">
         <is>
           <t>non</t>
         </is>
       </c>
-      <c r="I6" s="22" t="inlineStr">
+      <c r="I6" s="11" t="inlineStr">
         <is>
           <t>oui</t>
         </is>
       </c>
-      <c r="J6" s="11" t="inlineStr">
+      <c r="J6" s="12" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="K6" s="12" t="inlineStr">
-        <is>
-          <t>balises &lt;font&gt; (13) | non responsive | pas de @media | pas de flex/grid | pas de variables CSS | CSS tres court (434B) | aucun radius/ombre</t>
+      <c r="K6" s="13" t="inlineStr">
+        <is>
+          <t>balises &lt;font&gt; (2) | non responsive | pas de @media | pas de flex/grid | pas de variables CSS | CSS tres court (434B) | aucun radius/ombre</t>
         </is>
       </c>
     </row>
     <row r="7" ht="30" customHeight="1">
-      <c r="A7" s="13" t="inlineStr">
-        <is>
-          <t>atie-bat.fr</t>
-        </is>
-      </c>
-      <c r="B7" s="14" t="inlineStr">
-        <is>
-          <t>Atie Bat</t>
-        </is>
-      </c>
-      <c r="C7" s="15" t="inlineStr">
-        <is>
-          <t>Paris</t>
-        </is>
-      </c>
-      <c r="D7" s="16" t="inlineStr"/>
-      <c r="E7" s="17" t="inlineStr">
-        <is>
-          <t>75</t>
+      <c r="A7" s="14" t="inlineStr">
+        <is>
+          <t>biasini-electricite.com</t>
+        </is>
+      </c>
+      <c r="B7" s="15" t="inlineStr">
+        <is>
+          <t>Biasini</t>
+        </is>
+      </c>
+      <c r="C7" s="16" t="inlineStr">
+        <is>
+          <t>Toulouse</t>
+        </is>
+      </c>
+      <c r="D7" s="17" t="inlineStr"/>
+      <c r="E7" s="18" t="inlineStr">
+        <is>
+          <t>31</t>
         </is>
       </c>
       <c r="F7" s="9" t="n">
         <v>56</v>
       </c>
-      <c r="G7" s="17" t="n">
+      <c r="G7" s="18" t="n">
         <v>6</v>
       </c>
-      <c r="H7" s="18" t="inlineStr">
-        <is>
-          <t>non</t>
-        </is>
-      </c>
-      <c r="I7" s="19" t="inlineStr">
+      <c r="H7" s="19" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="I7" s="20" t="inlineStr">
         <is>
           <t>oui</t>
         </is>
       </c>
-      <c r="J7" s="20" t="inlineStr">
+      <c r="J7" s="21" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="K7" s="21" t="inlineStr">
-        <is>
-          <t>balises &lt;font&gt; (2) | non responsive | pas de @media | pas de flex/grid | pas de variables CSS | CSS tres court (434B) | aucun radius/ombre</t>
+      <c r="K7" s="22" t="inlineStr">
+        <is>
+          <t>balises &lt;font&gt; (1) | non responsive | pas de @media | pas de flex/grid | pas de variables CSS | CSS tres court (434B) | aucun radius/ombre</t>
         </is>
       </c>
     </row>
     <row r="8" ht="30" customHeight="1">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>biasini-electricite.com</t>
+          <t>tech-plomberie.fr</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>Biasini</t>
+          <t>Tec Plomberie</t>
         </is>
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>Toulouse</t>
+          <t>Orleans</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr"/>
       <c r="E8" s="8" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>45</t>
         </is>
       </c>
       <c r="F8" s="9" t="n">
@@ -909,117 +897,117 @@
           <t>non</t>
         </is>
       </c>
-      <c r="I8" s="22" t="inlineStr">
+      <c r="I8" s="11" t="inlineStr">
         <is>
           <t>oui</t>
         </is>
       </c>
-      <c r="J8" s="11" t="inlineStr">
+      <c r="J8" s="12" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="K8" s="12" t="inlineStr">
-        <is>
-          <t>balises &lt;font&gt; (1) | non responsive | pas de @media | pas de flex/grid | pas de variables CSS | CSS tres court (434B) | aucun radius/ombre</t>
+      <c r="K8" s="13" t="inlineStr">
+        <is>
+          <t>balises &lt;font&gt; (3) | non responsive | pas de @media | pas de flex/grid | pas de variables CSS | CSS tres court (434B) | aucun radius/ombre</t>
         </is>
       </c>
     </row>
     <row r="9" ht="30" customHeight="1">
-      <c r="A9" s="13" t="inlineStr">
-        <is>
-          <t>tech-plomberie.fr</t>
-        </is>
-      </c>
-      <c r="B9" s="14" t="inlineStr">
-        <is>
-          <t>Tec Plomberie</t>
-        </is>
-      </c>
-      <c r="C9" s="15" t="inlineStr">
-        <is>
-          <t>Orleans</t>
-        </is>
-      </c>
-      <c r="D9" s="16" t="inlineStr"/>
-      <c r="E9" s="17" t="inlineStr">
-        <is>
-          <t>45</t>
+      <c r="A9" s="14" t="inlineStr">
+        <is>
+          <t>espace-bois-66.com</t>
+        </is>
+      </c>
+      <c r="B9" s="15" t="inlineStr">
+        <is>
+          <t>Espace Bois Alu PVC</t>
+        </is>
+      </c>
+      <c r="C9" s="16" t="inlineStr">
+        <is>
+          <t>Perpignan</t>
+        </is>
+      </c>
+      <c r="D9" s="17" t="inlineStr"/>
+      <c r="E9" s="18" t="inlineStr">
+        <is>
+          <t>66</t>
         </is>
       </c>
       <c r="F9" s="9" t="n">
-        <v>56</v>
-      </c>
-      <c r="G9" s="17" t="n">
-        <v>6</v>
-      </c>
-      <c r="H9" s="18" t="inlineStr">
-        <is>
-          <t>non</t>
-        </is>
-      </c>
-      <c r="I9" s="19" t="inlineStr">
+        <v>55</v>
+      </c>
+      <c r="G9" s="18" t="n">
+        <v>3</v>
+      </c>
+      <c r="H9" s="19" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="I9" s="20" t="inlineStr">
         <is>
           <t>oui</t>
         </is>
       </c>
-      <c r="J9" s="20" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K9" s="21" t="inlineStr">
-        <is>
-          <t>balises &lt;font&gt; (3) | non responsive | pas de @media | pas de flex/grid | pas de variables CSS | CSS tres court (434B) | aucun radius/ombre</t>
+      <c r="J9" s="21" t="inlineStr">
+        <is>
+          <t>cfirsty®</t>
+        </is>
+      </c>
+      <c r="K9" s="22" t="inlineStr">
+        <is>
+          <t>layout en tableaux (9) | non responsive | pas de @media | pas de flex/grid | pas de variables CSS | police vintage</t>
         </is>
       </c>
     </row>
     <row r="10" ht="30" customHeight="1">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>verandaconcept.fr</t>
+          <t>fais-ci-fais-ca.com</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>Véranda Concept</t>
+          <t>Fais ci Fais ça</t>
         </is>
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Paris</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr"/>
       <c r="E10" s="8" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>75</t>
         </is>
       </c>
       <c r="F10" s="9" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G10" s="8" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="H10" s="10" t="inlineStr">
         <is>
           <t>non</t>
         </is>
       </c>
-      <c r="I10" s="22" t="inlineStr">
+      <c r="I10" s="11" t="inlineStr">
         <is>
           <t>oui</t>
         </is>
       </c>
-      <c r="J10" s="11" t="inlineStr">
-        <is>
-          <t>joomla! - copyright (c) 2005 - 2006 open source matters. all</t>
-        </is>
-      </c>
-      <c r="K10" s="12" t="inlineStr">
-        <is>
-          <t>layout en tableaux (7) | doctype ancien | non responsive | pas de @media | pas de flex/grid | aucun radius/ombre</t>
+      <c r="J10" s="12" t="inlineStr">
+        <is>
+          <t>wordpress 3.0.1</t>
+        </is>
+      </c>
+      <c r="K10" s="13" t="inlineStr">
+        <is>
+          <t>&lt;center&gt; | doctype ancien | non responsive | document.write | pas de @media | pas de flex/grid | pas de variables CSS | police vintage</t>
         </is>
       </c>
     </row>
@@ -1168,80 +1156,80 @@
           <t>non</t>
         </is>
       </c>
-      <c r="I4" s="22" t="inlineStr">
+      <c r="I4" s="11" t="inlineStr">
         <is>
           <t>oui</t>
         </is>
       </c>
-      <c r="J4" s="11" t="inlineStr">
+      <c r="J4" s="12" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="K4" s="12" t="inlineStr">
+      <c r="K4" s="13" t="inlineStr">
         <is>
           <t>layout en tableaux (9) | balises &lt;font&gt; (15) | sans doctype | non responsive | pas de @media | pas de flex/grid | pas de variables CSS | aucun radius/ombre</t>
         </is>
       </c>
     </row>
     <row r="5" ht="30" customHeight="1">
-      <c r="A5" s="13" t="inlineStr">
-        <is>
-          <t>ermontbienetre.fr</t>
-        </is>
-      </c>
-      <c r="B5" s="14" t="inlineStr">
-        <is>
-          <t>Esthétique et Massage de Bien-Être</t>
-        </is>
-      </c>
-      <c r="C5" s="15" t="inlineStr">
+      <c r="A5" s="14" t="inlineStr">
+        <is>
+          <t>thai-rachawadee.fr</t>
+        </is>
+      </c>
+      <c r="B5" s="15" t="inlineStr">
+        <is>
+          <t>Thaï Rachawadee</t>
+        </is>
+      </c>
+      <c r="C5" s="16" t="inlineStr">
         <is>
           <t>Paris</t>
         </is>
       </c>
-      <c r="D5" s="16" t="inlineStr"/>
-      <c r="E5" s="17" t="inlineStr">
+      <c r="D5" s="17" t="inlineStr"/>
+      <c r="E5" s="18" t="inlineStr">
         <is>
           <t>75</t>
         </is>
       </c>
       <c r="F5" s="9" t="n">
-        <v>68</v>
-      </c>
-      <c r="G5" s="17" t="n">
+        <v>66</v>
+      </c>
+      <c r="G5" s="18" t="n">
         <v>6</v>
       </c>
-      <c r="H5" s="18" t="inlineStr">
-        <is>
-          <t>non</t>
-        </is>
-      </c>
-      <c r="I5" s="19" t="inlineStr">
+      <c r="H5" s="19" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="I5" s="20" t="inlineStr">
         <is>
           <t>oui</t>
         </is>
       </c>
-      <c r="J5" s="20" t="inlineStr">
+      <c r="J5" s="21" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="K5" s="21" t="inlineStr">
-        <is>
-          <t>layout en tableaux (8) | bgcolor= | doctype ancien | non responsive | gif de mise en page | images .gif | pas de @media | pas de flex/grid | aucun radius/ombre</t>
+      <c r="K5" s="22" t="inlineStr">
+        <is>
+          <t>bgcolor= | frameset | sans doctype | non responsive | pas de @media | px uniquement | pas de flex/grid | pas de variables CSS | aucun radius/ombre</t>
         </is>
       </c>
     </row>
     <row r="6" ht="30" customHeight="1">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>thai-rachawadee.fr</t>
+          <t>atelier-arnaud-marie-coiffeur.fr</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>Thaï Rachawadee</t>
+          <t>Arnaud Marie</t>
         </is>
       </c>
       <c r="C6" s="6" t="inlineStr">
@@ -1256,7 +1244,7 @@
         </is>
       </c>
       <c r="F6" s="9" t="n">
-        <v>66</v>
+        <v>56</v>
       </c>
       <c r="G6" s="8" t="n">
         <v>6</v>
@@ -1266,95 +1254,95 @@
           <t>non</t>
         </is>
       </c>
-      <c r="I6" s="22" t="inlineStr">
+      <c r="I6" s="11" t="inlineStr">
         <is>
           <t>oui</t>
         </is>
       </c>
-      <c r="J6" s="11" t="inlineStr">
+      <c r="J6" s="12" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="K6" s="12" t="inlineStr">
-        <is>
-          <t>bgcolor= | frameset | sans doctype | non responsive | pas de @media | px uniquement | pas de flex/grid | pas de variables CSS | aucun radius/ombre</t>
+      <c r="K6" s="13" t="inlineStr">
+        <is>
+          <t>balises &lt;font&gt; (4) | non responsive | pas de @media | pas de flex/grid | pas de variables CSS | CSS tres court (434B) | aucun radius/ombre</t>
         </is>
       </c>
     </row>
     <row r="7" ht="30" customHeight="1">
-      <c r="A7" s="13" t="inlineStr">
-        <is>
-          <t>auxonglesdor.free.fr</t>
-        </is>
-      </c>
-      <c r="B7" s="14" t="inlineStr">
-        <is>
-          <t>Aux Ongles d'Or</t>
-        </is>
-      </c>
-      <c r="C7" s="15" t="inlineStr">
-        <is>
-          <t>Paris</t>
-        </is>
-      </c>
-      <c r="D7" s="16" t="inlineStr"/>
-      <c r="E7" s="17" t="inlineStr">
-        <is>
-          <t>75</t>
-        </is>
-      </c>
-      <c r="F7" s="9" t="n">
-        <v>58</v>
-      </c>
-      <c r="G7" s="17" t="n">
-        <v>10</v>
-      </c>
-      <c r="H7" s="18" t="inlineStr">
-        <is>
-          <t>non</t>
-        </is>
-      </c>
-      <c r="I7" s="18" t="inlineStr">
-        <is>
-          <t>non</t>
-        </is>
-      </c>
-      <c r="J7" s="20" t="inlineStr">
+      <c r="A7" s="14" t="inlineStr">
+        <is>
+          <t>florentina-linea.fr</t>
+        </is>
+      </c>
+      <c r="B7" s="15" t="inlineStr">
+        <is>
+          <t>Florentina</t>
+        </is>
+      </c>
+      <c r="C7" s="16" t="inlineStr">
+        <is>
+          <t>Nantes</t>
+        </is>
+      </c>
+      <c r="D7" s="17" t="inlineStr"/>
+      <c r="E7" s="18" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="F7" s="23" t="n">
+        <v>47</v>
+      </c>
+      <c r="G7" s="18" t="n">
+        <v>8</v>
+      </c>
+      <c r="H7" s="19" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="I7" s="19" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="J7" s="21" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="K7" s="21" t="inlineStr">
-        <is>
-          <t>&lt;center&gt; | doctype ancien | non responsive | gif de mise en page | pas de @media | pas de flex/grid | pas de variables CSS | police vintage | aucun radius/ombre</t>
+      <c r="K7" s="22" t="inlineStr">
+        <is>
+          <t>balises &lt;font&gt; (1) | non responsive | pas de @media | pas de flex/grid | pas de variables CSS</t>
         </is>
       </c>
     </row>
     <row r="8" ht="30" customHeight="1">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>mickaelgreg-coiffure.com</t>
+          <t>institut-beaute-doucebelle.fr</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>Salon Mixte Barneoud</t>
+          <t>Institut de Beauté Doucebelle</t>
         </is>
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>Marseille</t>
+          <t>Annemasse</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr"/>
       <c r="E8" s="8" t="inlineStr">
         <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="F8" s="9" t="n">
-        <v>58</v>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="F8" s="23" t="n">
+        <v>46</v>
       </c>
       <c r="G8" s="8" t="n">
         <v>3</v>
@@ -1364,117 +1352,117 @@
           <t>non</t>
         </is>
       </c>
-      <c r="I8" s="22" t="inlineStr">
+      <c r="I8" s="11" t="inlineStr">
         <is>
           <t>oui</t>
         </is>
       </c>
-      <c r="J8" s="11" t="inlineStr">
+      <c r="J8" s="12" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="K8" s="12" t="inlineStr">
-        <is>
-          <t>layout en tableaux (13) | doctype ancien | non responsive | pas de @media | pas de flex/grid | pas de variables CSS | aucun radius/ombre</t>
+      <c r="K8" s="13" t="inlineStr">
+        <is>
+          <t>non responsive | pas de @media | pas de flex/grid | pas de variables CSS | CSS tres court (434B) | aucun radius/ombre</t>
         </is>
       </c>
     </row>
     <row r="9" ht="30" customHeight="1">
-      <c r="A9" s="13" t="inlineStr">
-        <is>
-          <t>atelier-arnaud-marie-coiffeur.fr</t>
-        </is>
-      </c>
-      <c r="B9" s="14" t="inlineStr">
-        <is>
-          <t>Arnaud Marie</t>
-        </is>
-      </c>
-      <c r="C9" s="15" t="inlineStr">
-        <is>
-          <t>Paris</t>
-        </is>
-      </c>
-      <c r="D9" s="16" t="inlineStr"/>
-      <c r="E9" s="17" t="inlineStr">
-        <is>
-          <t>75</t>
-        </is>
-      </c>
-      <c r="F9" s="9" t="n">
-        <v>56</v>
-      </c>
-      <c r="G9" s="17" t="n">
-        <v>6</v>
-      </c>
-      <c r="H9" s="18" t="inlineStr">
-        <is>
-          <t>non</t>
-        </is>
-      </c>
-      <c r="I9" s="19" t="inlineStr">
+      <c r="A9" s="14" t="inlineStr">
+        <is>
+          <t>coiffurestyling.site-solocal.com</t>
+        </is>
+      </c>
+      <c r="B9" s="15" t="inlineStr">
+        <is>
+          <t>Styling</t>
+        </is>
+      </c>
+      <c r="C9" s="16" t="inlineStr">
+        <is>
+          <t>Nancy</t>
+        </is>
+      </c>
+      <c r="D9" s="17" t="inlineStr"/>
+      <c r="E9" s="18" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="F9" s="23" t="n">
+        <v>46</v>
+      </c>
+      <c r="G9" s="18" t="n">
+        <v>3</v>
+      </c>
+      <c r="H9" s="19" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="I9" s="20" t="inlineStr">
         <is>
           <t>oui</t>
         </is>
       </c>
-      <c r="J9" s="20" t="inlineStr">
+      <c r="J9" s="21" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="K9" s="21" t="inlineStr">
-        <is>
-          <t>balises &lt;font&gt; (4) | non responsive | pas de @media | pas de flex/grid | pas de variables CSS | CSS tres court (434B) | aucun radius/ombre</t>
+      <c r="K9" s="22" t="inlineStr">
+        <is>
+          <t>non responsive | pas de @media | pas de flex/grid | pas de variables CSS | CSS tres court (434B) | aucun radius/ombre</t>
         </is>
       </c>
     </row>
     <row r="10" ht="30" customHeight="1">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>florentina-linea.fr</t>
+          <t>correiamanuelcoiffeurcreateur.site-solocal.com</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>Florentina</t>
+          <t>Mannuel Correia</t>
         </is>
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>Nantes</t>
+          <t>Lyon</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr"/>
       <c r="E10" s="8" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>69</t>
         </is>
       </c>
       <c r="F10" s="23" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="G10" s="8" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="H10" s="10" t="inlineStr">
         <is>
           <t>non</t>
         </is>
       </c>
-      <c r="I10" s="10" t="inlineStr">
-        <is>
-          <t>non</t>
-        </is>
-      </c>
-      <c r="J10" s="11" t="inlineStr">
+      <c r="I10" s="11" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="J10" s="12" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="K10" s="12" t="inlineStr">
-        <is>
-          <t>balises &lt;font&gt; (1) | non responsive | pas de @media | pas de flex/grid | pas de variables CSS</t>
+      <c r="K10" s="13" t="inlineStr">
+        <is>
+          <t>non responsive | pas de @media | pas de flex/grid | pas de variables CSS | CSS tres court (434B) | aucun radius/ombre</t>
         </is>
       </c>
     </row>
@@ -1623,40 +1611,40 @@
           <t>non</t>
         </is>
       </c>
-      <c r="I4" s="22" t="inlineStr">
+      <c r="I4" s="11" t="inlineStr">
         <is>
           <t>oui</t>
         </is>
       </c>
-      <c r="J4" s="11" t="inlineStr">
+      <c r="J4" s="12" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="K4" s="12" t="inlineStr">
+      <c r="K4" s="13" t="inlineStr">
         <is>
           <t>balises &lt;font&gt; (5) | non responsive | document.write | pas de @media | pas de flex/grid | pas de variables CSS | CSS tres court (3B) | aucun radius/ombre</t>
         </is>
       </c>
     </row>
     <row r="5" ht="30" customHeight="1">
-      <c r="A5" s="13" t="inlineStr">
+      <c r="A5" s="14" t="inlineStr">
         <is>
           <t>chezmario.fr</t>
         </is>
       </c>
-      <c r="B5" s="14" t="inlineStr">
+      <c r="B5" s="15" t="inlineStr">
         <is>
           <t>Chez Mario</t>
         </is>
       </c>
-      <c r="C5" s="15" t="inlineStr">
+      <c r="C5" s="16" t="inlineStr">
         <is>
           <t>Bordeaux</t>
         </is>
       </c>
-      <c r="D5" s="16" t="inlineStr"/>
-      <c r="E5" s="17" t="inlineStr">
+      <c r="D5" s="17" t="inlineStr"/>
+      <c r="E5" s="18" t="inlineStr">
         <is>
           <t>33</t>
         </is>
@@ -1664,25 +1652,25 @@
       <c r="F5" s="9" t="n">
         <v>58</v>
       </c>
-      <c r="G5" s="17" t="n">
+      <c r="G5" s="18" t="n">
         <v>5</v>
       </c>
-      <c r="H5" s="18" t="inlineStr">
-        <is>
-          <t>non</t>
-        </is>
-      </c>
-      <c r="I5" s="18" t="inlineStr">
-        <is>
-          <t>non</t>
-        </is>
-      </c>
-      <c r="J5" s="20" t="inlineStr">
+      <c r="H5" s="19" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="I5" s="19" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="J5" s="21" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="K5" s="21" t="inlineStr">
+      <c r="K5" s="22" t="inlineStr">
         <is>
           <t>layout en tableaux (4) | doctype ancien | non responsive | pas de @media | pas de flex/grid | pas de variables CSS | aucun radius/ombre</t>
         </is>
@@ -1691,110 +1679,110 @@
     <row r="6" ht="30" customHeight="1">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>baan.fr</t>
+          <t>azur-traiteur.fr</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>Baan Siam</t>
+          <t>Azur Traiteur</t>
         </is>
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>Toulouse</t>
+          <t>Aix-en-Provence</t>
         </is>
       </c>
       <c r="D6" s="7" t="inlineStr"/>
       <c r="E6" s="8" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>13</t>
         </is>
       </c>
       <c r="F6" s="9" t="n">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="G6" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="H6" s="10" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="I6" s="11" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="J6" s="12" t="inlineStr">
+        <is>
+          <t>joomla! 1.5 - open source content management</t>
+        </is>
+      </c>
+      <c r="K6" s="13" t="inlineStr">
+        <is>
+          <t>layout en tableaux (7) | doctype ancien | non responsive | pas de @media | pas de flex/grid</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="30" customHeight="1">
+      <c r="A7" s="14" t="inlineStr">
+        <is>
+          <t>happy-pizz.com</t>
+        </is>
+      </c>
+      <c r="B7" s="15" t="inlineStr">
+        <is>
+          <t>Happy Pizz - Chez Jo</t>
+        </is>
+      </c>
+      <c r="C7" s="16" t="inlineStr">
+        <is>
+          <t>Quimper</t>
+        </is>
+      </c>
+      <c r="D7" s="17" t="inlineStr"/>
+      <c r="E7" s="18" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="F7" s="23" t="n">
+        <v>49</v>
+      </c>
+      <c r="G7" s="18" t="n">
         <v>6</v>
       </c>
-      <c r="H6" s="10" t="inlineStr">
-        <is>
-          <t>non</t>
-        </is>
-      </c>
-      <c r="I6" s="22" t="inlineStr">
+      <c r="H7" s="19" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="I7" s="20" t="inlineStr">
         <is>
           <t>oui</t>
         </is>
       </c>
-      <c r="J6" s="11" t="inlineStr">
+      <c r="J7" s="21" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="K6" s="12" t="inlineStr">
-        <is>
-          <t>layout en tableaux (9) | balises &lt;font&gt; (32) | &lt;center&gt; | bgcolor= | sans doctype | non responsive | images .gif</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="30" customHeight="1">
-      <c r="A7" s="13" t="inlineStr">
-        <is>
-          <t>lechateausormiou.fr</t>
-        </is>
-      </c>
-      <c r="B7" s="14" t="inlineStr">
-        <is>
-          <t>Le Château Sormiou</t>
-        </is>
-      </c>
-      <c r="C7" s="15" t="inlineStr">
-        <is>
-          <t>Marseille</t>
-        </is>
-      </c>
-      <c r="D7" s="16" t="inlineStr"/>
-      <c r="E7" s="17" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="F7" s="23" t="n">
-        <v>47</v>
-      </c>
-      <c r="G7" s="17" t="n">
-        <v>8</v>
-      </c>
-      <c r="H7" s="18" t="inlineStr">
-        <is>
-          <t>non</t>
-        </is>
-      </c>
-      <c r="I7" s="18" t="inlineStr">
-        <is>
-          <t>non</t>
-        </is>
-      </c>
-      <c r="J7" s="20" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K7" s="21" t="inlineStr">
-        <is>
-          <t>balises &lt;font&gt; (1) | non responsive | pas de @media | pas de flex/grid | pas de variables CSS</t>
+      <c r="K7" s="22" t="inlineStr">
+        <is>
+          <t>bgcolor= | doctype ancien | non responsive | pas de @media | pas de flex/grid | pas de variables CSS | aucun radius/ombre</t>
         </is>
       </c>
     </row>
     <row r="8" ht="30" customHeight="1">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>ldvdraveil.fr</t>
+          <t>boucherie-economique.fr</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>La Dolce Vita</t>
+          <t>La boucherie économique</t>
         </is>
       </c>
       <c r="C8" s="6" t="inlineStr">
@@ -1802,138 +1790,134 @@
           <t>Paris</t>
         </is>
       </c>
-      <c r="D8" s="24" t="inlineStr">
-        <is>
-          <t>Draveil (91210)</t>
-        </is>
-      </c>
+      <c r="D8" s="7" t="inlineStr"/>
       <c r="E8" s="8" t="inlineStr">
         <is>
           <t>75</t>
         </is>
       </c>
       <c r="F8" s="23" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="G8" s="8" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H8" s="10" t="inlineStr">
         <is>
           <t>non</t>
         </is>
       </c>
-      <c r="I8" s="22" t="inlineStr">
+      <c r="I8" s="11" t="inlineStr">
         <is>
           <t>oui</t>
         </is>
       </c>
-      <c r="J8" s="11" t="inlineStr">
+      <c r="J8" s="12" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="K8" s="12" t="inlineStr">
-        <is>
-          <t>layout en tableaux (29) | balises &lt;font&gt; (4) | &lt;center&gt; | non responsive | &lt;br&gt; en masse</t>
+      <c r="K8" s="13" t="inlineStr">
+        <is>
+          <t>non responsive | pas de @media | pas de flex/grid | pas de variables CSS | CSS tres court (434B) | aucun radius/ombre</t>
         </is>
       </c>
     </row>
     <row r="9" ht="30" customHeight="1">
-      <c r="A9" s="13" t="inlineStr">
-        <is>
-          <t>chapitre6.fr</t>
-        </is>
-      </c>
-      <c r="B9" s="14" t="inlineStr">
-        <is>
-          <t>Chapitre VI</t>
-        </is>
-      </c>
-      <c r="C9" s="15" t="inlineStr">
-        <is>
-          <t>Lille</t>
-        </is>
-      </c>
-      <c r="D9" s="16" t="inlineStr"/>
-      <c r="E9" s="17" t="inlineStr">
-        <is>
-          <t>59</t>
+      <c r="A9" s="14" t="inlineStr">
+        <is>
+          <t>coignacsarl.site-solocal.com</t>
+        </is>
+      </c>
+      <c r="B9" s="15" t="inlineStr">
+        <is>
+          <t>Maison Coignac</t>
+        </is>
+      </c>
+      <c r="C9" s="16" t="inlineStr">
+        <is>
+          <t>Limoges</t>
+        </is>
+      </c>
+      <c r="D9" s="17" t="inlineStr"/>
+      <c r="E9" s="18" t="inlineStr">
+        <is>
+          <t>87</t>
         </is>
       </c>
       <c r="F9" s="23" t="n">
-        <v>45</v>
-      </c>
-      <c r="G9" s="17" t="n">
-        <v>8</v>
-      </c>
-      <c r="H9" s="18" t="inlineStr">
-        <is>
-          <t>non</t>
-        </is>
-      </c>
-      <c r="I9" s="18" t="inlineStr">
-        <is>
-          <t>non</t>
-        </is>
-      </c>
-      <c r="J9" s="20" t="inlineStr">
+        <v>46</v>
+      </c>
+      <c r="G9" s="18" t="n">
+        <v>3</v>
+      </c>
+      <c r="H9" s="19" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="I9" s="20" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="J9" s="21" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="K9" s="21" t="inlineStr">
-        <is>
-          <t>balises &lt;font&gt; (1) | bgcolor= | frameset | sans doctype | non responsive</t>
+      <c r="K9" s="22" t="inlineStr">
+        <is>
+          <t>non responsive | pas de @media | pas de flex/grid | pas de variables CSS | CSS tres court (434B) | aucun radius/ombre</t>
         </is>
       </c>
     </row>
     <row r="10" ht="30" customHeight="1">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>laovientiane.fr</t>
+          <t>chapitre6.fr</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>Lao Vientiane</t>
+          <t>Chapitre VI</t>
         </is>
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>Nice</t>
+          <t>Lille</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr"/>
       <c r="E10" s="8" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>59</t>
         </is>
       </c>
       <c r="F10" s="23" t="n">
         <v>45</v>
       </c>
       <c r="G10" s="8" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="H10" s="10" t="inlineStr">
         <is>
           <t>non</t>
         </is>
       </c>
-      <c r="I10" s="22" t="inlineStr">
-        <is>
-          <t>oui</t>
-        </is>
-      </c>
-      <c r="J10" s="11" t="inlineStr">
+      <c r="I10" s="10" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="J10" s="12" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="K10" s="12" t="inlineStr">
-        <is>
-          <t>&lt;center&gt; | non responsive | pas de @media | pas de flex/grid | pas de variables CSS | aucun radius/ombre</t>
+      <c r="K10" s="13" t="inlineStr">
+        <is>
+          <t>balises &lt;font&gt; (1) | bgcolor= | frameset | sans doctype | non responsive</t>
         </is>
       </c>
     </row>
@@ -2087,308 +2071,308 @@
           <t>non</t>
         </is>
       </c>
-      <c r="J4" s="11" t="inlineStr">
+      <c r="J4" s="12" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="K4" s="12" t="inlineStr">
+      <c r="K4" s="13" t="inlineStr">
         <is>
           <t>layout en tableaux (5) | balises &lt;font&gt; (1) | doctype ancien | non responsive | gif de mise en page | images .gif | pas de @media | px uniquement | pas de flex/grid | pas de variables CSS | aucun radius/ombre</t>
         </is>
       </c>
     </row>
     <row r="5" ht="30" customHeight="1">
-      <c r="A5" s="13" t="inlineStr">
-        <is>
-          <t>garage-laban-rouen.fr</t>
-        </is>
-      </c>
-      <c r="B5" s="14" t="inlineStr">
-        <is>
-          <t>Garage Laban</t>
-        </is>
-      </c>
-      <c r="C5" s="15" t="inlineStr">
-        <is>
-          <t>Rouen</t>
-        </is>
-      </c>
-      <c r="D5" s="16" t="inlineStr"/>
-      <c r="E5" s="17" t="inlineStr">
-        <is>
-          <t>76</t>
+      <c r="A5" s="14" t="inlineStr">
+        <is>
+          <t>belr-automobiles.com</t>
+        </is>
+      </c>
+      <c r="B5" s="15" t="inlineStr">
+        <is>
+          <t>Bel'R Automobiles</t>
+        </is>
+      </c>
+      <c r="C5" s="16" t="inlineStr">
+        <is>
+          <t>La Rochelle</t>
+        </is>
+      </c>
+      <c r="D5" s="17" t="inlineStr"/>
+      <c r="E5" s="18" t="inlineStr">
+        <is>
+          <t>17</t>
         </is>
       </c>
       <c r="F5" s="9" t="n">
-        <v>56</v>
-      </c>
-      <c r="G5" s="17" t="n">
+        <v>50</v>
+      </c>
+      <c r="G5" s="18" t="n">
         <v>6</v>
       </c>
-      <c r="H5" s="18" t="inlineStr">
-        <is>
-          <t>non</t>
-        </is>
-      </c>
-      <c r="I5" s="19" t="inlineStr">
+      <c r="H5" s="19" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="I5" s="20" t="inlineStr">
         <is>
           <t>oui</t>
         </is>
       </c>
-      <c r="J5" s="20" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K5" s="21" t="inlineStr">
-        <is>
-          <t>balises &lt;font&gt; (16) | non responsive | pas de @media | pas de flex/grid | pas de variables CSS | CSS tres court (434B) | aucun radius/ombre</t>
+      <c r="J5" s="21" t="inlineStr">
+        <is>
+          <t>lmsoft web creator pro, version:6.0.0.4</t>
+        </is>
+      </c>
+      <c r="K5" s="22" t="inlineStr">
+        <is>
+          <t>balises &lt;font&gt; (29) | non responsive | pas de @media | pas de flex/grid | pas de variables CSS | aucun radius/ombre</t>
         </is>
       </c>
     </row>
     <row r="6" ht="30" customHeight="1">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>autopieces35.fr</t>
+          <t>autopremium-66.fr</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>Auto Pièces 35</t>
+          <t>Top Garage Auto Premium 66</t>
         </is>
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>Rennes</t>
+          <t>Perpignan</t>
         </is>
       </c>
       <c r="D6" s="7" t="inlineStr"/>
       <c r="E6" s="8" t="inlineStr">
         <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="F6" s="9" t="n">
-        <v>56</v>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="F6" s="23" t="n">
+        <v>46</v>
       </c>
       <c r="G6" s="8" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H6" s="10" t="inlineStr">
         <is>
           <t>non</t>
         </is>
       </c>
-      <c r="I6" s="22" t="inlineStr">
+      <c r="I6" s="11" t="inlineStr">
         <is>
           <t>oui</t>
         </is>
       </c>
-      <c r="J6" s="11" t="inlineStr">
+      <c r="J6" s="12" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="K6" s="12" t="inlineStr">
-        <is>
-          <t>balises &lt;font&gt; (10) | non responsive | pas de @media | pas de flex/grid | pas de variables CSS | CSS tres court (434B) | aucun radius/ombre</t>
+      <c r="K6" s="13" t="inlineStr">
+        <is>
+          <t>non responsive | pas de @media | pas de flex/grid | pas de variables CSS | CSS tres court (434B) | aucun radius/ombre</t>
         </is>
       </c>
     </row>
     <row r="7" ht="30" customHeight="1">
-      <c r="A7" s="13" t="inlineStr">
-        <is>
-          <t>carrosserie-adamo.com</t>
-        </is>
-      </c>
-      <c r="B7" s="14" t="inlineStr">
-        <is>
-          <t>Carrosserie Adamo</t>
-        </is>
-      </c>
-      <c r="C7" s="15" t="inlineStr">
+      <c r="A7" s="14" t="inlineStr">
+        <is>
+          <t>garage-des-mines.fr</t>
+        </is>
+      </c>
+      <c r="B7" s="15" t="inlineStr">
+        <is>
+          <t>Garage des Mines</t>
+        </is>
+      </c>
+      <c r="C7" s="16" t="inlineStr">
         <is>
           <t>Saint-Etienne</t>
         </is>
       </c>
-      <c r="D7" s="16" t="inlineStr"/>
-      <c r="E7" s="17" t="inlineStr">
+      <c r="D7" s="17" t="inlineStr"/>
+      <c r="E7" s="18" t="inlineStr">
         <is>
           <t>42</t>
         </is>
       </c>
-      <c r="F7" s="9" t="n">
-        <v>56</v>
-      </c>
-      <c r="G7" s="17" t="n">
-        <v>6</v>
-      </c>
-      <c r="H7" s="18" t="inlineStr">
-        <is>
-          <t>non</t>
-        </is>
-      </c>
-      <c r="I7" s="19" t="inlineStr">
+      <c r="F7" s="23" t="n">
+        <v>46</v>
+      </c>
+      <c r="G7" s="18" t="n">
+        <v>3</v>
+      </c>
+      <c r="H7" s="19" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="I7" s="20" t="inlineStr">
         <is>
           <t>oui</t>
         </is>
       </c>
-      <c r="J7" s="20" t="inlineStr">
+      <c r="J7" s="21" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="K7" s="21" t="inlineStr">
-        <is>
-          <t>balises &lt;font&gt; (31) | non responsive | pas de @media | pas de flex/grid | pas de variables CSS | CSS tres court (434B) | aucun radius/ombre</t>
+      <c r="K7" s="22" t="inlineStr">
+        <is>
+          <t>non responsive | pas de @media | pas de flex/grid | pas de variables CSS | CSS tres court (434B) | aucun radius/ombre</t>
         </is>
       </c>
     </row>
     <row r="8" ht="30" customHeight="1">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>carrosserie-barcelona.fr</t>
+          <t>garageabauto.site-solocal.com</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>Carrosserie Barcelona</t>
+          <t>AB Auto</t>
         </is>
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>Bayonne</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr"/>
       <c r="E8" s="8" t="inlineStr">
         <is>
-          <t>64</t>
-        </is>
-      </c>
-      <c r="F8" s="9" t="n">
-        <v>56</v>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="F8" s="23" t="n">
+        <v>46</v>
       </c>
       <c r="G8" s="8" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H8" s="10" t="inlineStr">
         <is>
           <t>non</t>
         </is>
       </c>
-      <c r="I8" s="22" t="inlineStr">
+      <c r="I8" s="11" t="inlineStr">
         <is>
           <t>oui</t>
         </is>
       </c>
-      <c r="J8" s="11" t="inlineStr">
+      <c r="J8" s="12" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="K8" s="12" t="inlineStr">
-        <is>
-          <t>balises &lt;font&gt; (5) | non responsive | pas de @media | pas de flex/grid | pas de variables CSS | CSS tres court (434B) | aucun radius/ombre</t>
+      <c r="K8" s="13" t="inlineStr">
+        <is>
+          <t>non responsive | pas de @media | pas de flex/grid | pas de variables CSS | CSS tres court (434B) | aucun radius/ombre</t>
         </is>
       </c>
     </row>
     <row r="9" ht="30" customHeight="1">
-      <c r="A9" s="13" t="inlineStr">
-        <is>
-          <t>carrosserievernoise.fr</t>
-        </is>
-      </c>
-      <c r="B9" s="14" t="inlineStr">
-        <is>
-          <t>Carrosserie Vernoise</t>
-        </is>
-      </c>
-      <c r="C9" s="15" t="inlineStr">
-        <is>
-          <t>Rennes</t>
-        </is>
-      </c>
-      <c r="D9" s="16" t="inlineStr"/>
-      <c r="E9" s="17" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="F9" s="9" t="n">
-        <v>56</v>
-      </c>
-      <c r="G9" s="17" t="n">
-        <v>6</v>
-      </c>
-      <c r="H9" s="18" t="inlineStr">
-        <is>
-          <t>non</t>
-        </is>
-      </c>
-      <c r="I9" s="19" t="inlineStr">
+      <c r="A9" s="14" t="inlineStr">
+        <is>
+          <t>garagedelapaix.site-solocal.com</t>
+        </is>
+      </c>
+      <c r="B9" s="15" t="inlineStr">
+        <is>
+          <t>Garage de la Paix</t>
+        </is>
+      </c>
+      <c r="C9" s="16" t="inlineStr">
+        <is>
+          <t>Paris</t>
+        </is>
+      </c>
+      <c r="D9" s="17" t="inlineStr"/>
+      <c r="E9" s="18" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="F9" s="23" t="n">
+        <v>46</v>
+      </c>
+      <c r="G9" s="18" t="n">
+        <v>3</v>
+      </c>
+      <c r="H9" s="19" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="I9" s="20" t="inlineStr">
         <is>
           <t>oui</t>
         </is>
       </c>
-      <c r="J9" s="20" t="inlineStr">
+      <c r="J9" s="21" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="K9" s="21" t="inlineStr">
-        <is>
-          <t>balises &lt;font&gt; (7) | non responsive | pas de @media | pas de flex/grid | pas de variables CSS | CSS tres court (434B) | aucun radius/ombre</t>
+      <c r="K9" s="22" t="inlineStr">
+        <is>
+          <t>non responsive | pas de @media | pas de flex/grid | pas de variables CSS | CSS tres court (434B) | aucun radius/ombre</t>
         </is>
       </c>
     </row>
     <row r="10" ht="30" customHeight="1">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>belr-automobiles.com</t>
+          <t>ad69.fr</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>Bel'R Automobiles</t>
+          <t>AutoDiscount 69</t>
         </is>
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>La Rochelle</t>
+          <t>Lyon</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr"/>
       <c r="E10" s="8" t="inlineStr">
         <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="F10" s="9" t="n">
-        <v>50</v>
+          <t>69</t>
+        </is>
+      </c>
+      <c r="F10" s="23" t="n">
+        <v>42</v>
       </c>
       <c r="G10" s="8" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H10" s="10" t="inlineStr">
         <is>
           <t>non</t>
         </is>
       </c>
-      <c r="I10" s="22" t="inlineStr">
+      <c r="I10" s="11" t="inlineStr">
         <is>
           <t>oui</t>
         </is>
       </c>
-      <c r="J10" s="11" t="inlineStr">
-        <is>
-          <t>lmsoft web creator pro, version:6.0.0.4</t>
-        </is>
-      </c>
-      <c r="K10" s="12" t="inlineStr">
-        <is>
-          <t>balises &lt;font&gt; (29) | non responsive | pas de @media | pas de flex/grid | pas de variables CSS | aucun radius/ombre</t>
+      <c r="J10" s="12" t="inlineStr">
+        <is>
+          <t>webdev</t>
+        </is>
+      </c>
+      <c r="K10" s="13" t="inlineStr">
+        <is>
+          <t>layout en tableaux (193) | non responsive | document.write | pas de flex/grid | police vintage</t>
         </is>
       </c>
     </row>
@@ -2507,12 +2491,12 @@
     <row r="4" ht="30" customHeight="1">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>velocipaide.fr</t>
+          <t>sapah.fr</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>Vélocipaide</t>
+          <t>Sapah</t>
         </is>
       </c>
       <c r="C4" s="6" t="inlineStr">
@@ -2527,82 +2511,78 @@
         </is>
       </c>
       <c r="F4" s="9" t="n">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="G4" s="8" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="H4" s="10" t="inlineStr">
         <is>
           <t>non</t>
         </is>
       </c>
-      <c r="I4" s="22" t="inlineStr">
+      <c r="I4" s="10" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="J4" s="12" t="inlineStr">
+        <is>
+          <t>dreamweaver cs4, photoshop cs4, firework cs4</t>
+        </is>
+      </c>
+      <c r="K4" s="13" t="inlineStr">
+        <is>
+          <t>doctype ancien | non responsive | gif de mise en page | images .gif | document.write | pas de @media | pas de flex/grid | pas de variables CSS</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="30" customHeight="1">
+      <c r="A5" s="14" t="inlineStr">
+        <is>
+          <t>abaqueinformatique.com</t>
+        </is>
+      </c>
+      <c r="B5" s="15" t="inlineStr">
+        <is>
+          <t>@baque Informatique</t>
+        </is>
+      </c>
+      <c r="C5" s="16" t="inlineStr">
+        <is>
+          <t>La Rochelle</t>
+        </is>
+      </c>
+      <c r="D5" s="17" t="inlineStr"/>
+      <c r="E5" s="18" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="F5" s="9" t="n">
+        <v>51</v>
+      </c>
+      <c r="G5" s="18" t="n">
+        <v>3</v>
+      </c>
+      <c r="H5" s="19" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="I5" s="20" t="inlineStr">
         <is>
           <t>oui</t>
         </is>
       </c>
-      <c r="J4" s="11" t="inlineStr">
-        <is>
-          <t>bueno 1.5.1</t>
-        </is>
-      </c>
-      <c r="K4" s="12" t="inlineStr">
-        <is>
-          <t>&lt;center&gt; | bgcolor= | doctype ancien | non responsive | pas de @media | pas de flex/grid | pas de variables CSS | CSS tres court (2B) | aucun radius/ombre</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="30" customHeight="1">
-      <c r="A5" s="13" t="inlineStr">
-        <is>
-          <t>atelierdumenager.com</t>
-        </is>
-      </c>
-      <c r="B5" s="14" t="inlineStr">
-        <is>
-          <t>Atelier du ménager</t>
-        </is>
-      </c>
-      <c r="C5" s="15" t="inlineStr">
-        <is>
-          <t>Poitiers</t>
-        </is>
-      </c>
-      <c r="D5" s="25" t="inlineStr">
-        <is>
-          <t>Poitiers (86000)</t>
-        </is>
-      </c>
-      <c r="E5" s="17" t="inlineStr">
-        <is>
-          <t>86</t>
-        </is>
-      </c>
-      <c r="F5" s="9" t="n">
-        <v>56</v>
-      </c>
-      <c r="G5" s="17" t="n">
-        <v>6</v>
-      </c>
-      <c r="H5" s="18" t="inlineStr">
-        <is>
-          <t>non</t>
-        </is>
-      </c>
-      <c r="I5" s="19" t="inlineStr">
-        <is>
-          <t>oui</t>
-        </is>
-      </c>
-      <c r="J5" s="20" t="inlineStr">
+      <c r="J5" s="21" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="K5" s="21" t="inlineStr">
-        <is>
-          <t>balises &lt;font&gt; (2) | non responsive | pas de @media | pas de flex/grid | pas de variables CSS | CSS tres court (434B) | aucun radius/ombre</t>
+      <c r="K5" s="22" t="inlineStr">
+        <is>
+          <t>doctype ancien | non responsive | images .gif | pas de @media | pas de flex/grid | pas de variables CSS | police vintage | aucun radius/ombre</t>
         </is>
       </c>
     </row>
@@ -2644,173 +2624,173 @@
           <t>non</t>
         </is>
       </c>
-      <c r="J6" s="11" t="inlineStr">
+      <c r="J6" s="12" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="K6" s="12" t="inlineStr">
+      <c r="K6" s="13" t="inlineStr">
         <is>
           <t>&lt;center&gt; | doctype ancien | non responsive | pas de @media | pas de flex/grid | pas de variables CSS | aucun radius/ombre</t>
         </is>
       </c>
     </row>
     <row r="7" ht="30" customHeight="1">
-      <c r="A7" s="13" t="inlineStr">
-        <is>
-          <t>rustine-beaulieu.weebly.com</t>
-        </is>
-      </c>
-      <c r="B7" s="14" t="inlineStr">
-        <is>
-          <t>La Rustine de Beaulieu</t>
-        </is>
-      </c>
-      <c r="C7" s="15" t="inlineStr">
-        <is>
-          <t>Rennes</t>
-        </is>
-      </c>
-      <c r="D7" s="16" t="inlineStr"/>
-      <c r="E7" s="17" t="inlineStr">
-        <is>
-          <t>35</t>
+      <c r="A7" s="14" t="inlineStr">
+        <is>
+          <t>coeur-de-poil.fr</t>
+        </is>
+      </c>
+      <c r="B7" s="15" t="inlineStr">
+        <is>
+          <t>Cœur de Poil</t>
+        </is>
+      </c>
+      <c r="C7" s="16" t="inlineStr">
+        <is>
+          <t>Nancy</t>
+        </is>
+      </c>
+      <c r="D7" s="17" t="inlineStr"/>
+      <c r="E7" s="18" t="inlineStr">
+        <is>
+          <t>54</t>
         </is>
       </c>
       <c r="F7" s="23" t="n">
-        <v>49</v>
-      </c>
-      <c r="G7" s="17" t="n">
+        <v>46</v>
+      </c>
+      <c r="G7" s="18" t="n">
         <v>3</v>
       </c>
       <c r="H7" s="19" t="inlineStr">
         <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="I7" s="20" t="inlineStr">
+        <is>
           <t>oui</t>
         </is>
       </c>
-      <c r="I7" s="19" t="inlineStr">
-        <is>
-          <t>oui</t>
-        </is>
-      </c>
-      <c r="J7" s="20" t="inlineStr">
+      <c r="J7" s="21" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="K7" s="21" t="inlineStr">
-        <is>
-          <t>layout en tableaux (4) | balises &lt;font&gt; (29) | pas de @media | pas de flex/grid | pas de variables CSS | aucun radius/ombre</t>
+      <c r="K7" s="22" t="inlineStr">
+        <is>
+          <t>non responsive | pas de @media | pas de flex/grid | pas de variables CSS | CSS tres court (434B) | aucun radius/ombre</t>
         </is>
       </c>
     </row>
     <row r="8" ht="30" customHeight="1">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>velosapiens.fr</t>
+          <t>label-image-78.com</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>Vélo-Sapiens</t>
+          <t>Label Im@ge 78</t>
         </is>
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>Marseille</t>
+          <t>Paris</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr"/>
       <c r="E8" s="8" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>75</t>
         </is>
       </c>
       <c r="F8" s="23" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="G8" s="8" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H8" s="10" t="inlineStr">
         <is>
           <t>non</t>
         </is>
       </c>
-      <c r="I8" s="22" t="inlineStr">
+      <c r="I8" s="11" t="inlineStr">
         <is>
           <t>oui</t>
         </is>
       </c>
-      <c r="J8" s="11" t="inlineStr">
+      <c r="J8" s="12" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="K8" s="12" t="inlineStr">
-        <is>
-          <t>&lt;center&gt; | non responsive | pas de @media | pas de flex/grid | pas de variables CSS | aucun radius/ombre</t>
+      <c r="K8" s="13" t="inlineStr">
+        <is>
+          <t>doctype ancien | non responsive | pas de @media | pas de flex/grid | pas de variables CSS | aucun radius/ombre</t>
         </is>
       </c>
     </row>
     <row r="9" ht="30" customHeight="1">
-      <c r="A9" s="13" t="inlineStr">
-        <is>
-          <t>jpcycles.sitego.fr</t>
-        </is>
-      </c>
-      <c r="B9" s="14" t="inlineStr">
-        <is>
-          <t>JP Cycles</t>
-        </is>
-      </c>
-      <c r="C9" s="15" t="inlineStr">
-        <is>
-          <t>Paris</t>
-        </is>
-      </c>
-      <c r="D9" s="16" t="inlineStr"/>
-      <c r="E9" s="17" t="inlineStr">
-        <is>
-          <t>75</t>
+      <c r="A9" s="14" t="inlineStr">
+        <is>
+          <t>lypart-studio.com</t>
+        </is>
+      </c>
+      <c r="B9" s="15" t="inlineStr">
+        <is>
+          <t>Lypa'rt Studio</t>
+        </is>
+      </c>
+      <c r="C9" s="16" t="inlineStr">
+        <is>
+          <t>Le Mans</t>
+        </is>
+      </c>
+      <c r="D9" s="17" t="inlineStr"/>
+      <c r="E9" s="18" t="inlineStr">
+        <is>
+          <t>72</t>
         </is>
       </c>
       <c r="F9" s="23" t="n">
-        <v>37</v>
-      </c>
-      <c r="G9" s="17" t="n">
+        <v>42</v>
+      </c>
+      <c r="G9" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="H9" s="18" t="inlineStr">
-        <is>
-          <t>non</t>
-        </is>
-      </c>
-      <c r="I9" s="19" t="inlineStr">
+      <c r="H9" s="19" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="I9" s="20" t="inlineStr">
         <is>
           <t>oui</t>
         </is>
       </c>
-      <c r="J9" s="20" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K9" s="21" t="inlineStr">
-        <is>
-          <t>non responsive | pas de @media | pas de flex/grid | pas de variables CSS</t>
+      <c r="J9" s="21" t="inlineStr">
+        <is>
+          <t>webacappella 4.6.27  professional (osx) #22c4</t>
+        </is>
+      </c>
+      <c r="K9" s="22" t="inlineStr">
+        <is>
+          <t>doctype ancien | non responsive | document.write | pas de @media | pas de flex/grid</t>
         </is>
       </c>
     </row>
     <row r="10" ht="30" customHeight="1">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>archphoenix.team</t>
+          <t>jpcycles.sitego.fr</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>ArchPhénix Team (Atelier de Paris)</t>
+          <t>JP Cycles</t>
         </is>
       </c>
       <c r="C10" s="6" t="inlineStr">
@@ -2825,29 +2805,29 @@
         </is>
       </c>
       <c r="F10" s="23" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G10" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="H10" s="22" t="inlineStr">
+        <v>3</v>
+      </c>
+      <c r="H10" s="10" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="I10" s="11" t="inlineStr">
         <is>
           <t>oui</t>
         </is>
       </c>
-      <c r="I10" s="22" t="inlineStr">
-        <is>
-          <t>oui</t>
-        </is>
-      </c>
-      <c r="J10" s="11" t="inlineStr">
+      <c r="J10" s="12" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="K10" s="12" t="inlineStr">
-        <is>
-          <t>layout en tableaux (3) | pas de @media | pas de flex/grid | aucun radius/ombre</t>
+      <c r="K10" s="13" t="inlineStr">
+        <is>
+          <t>non responsive | pas de @media | pas de flex/grid | pas de variables CSS</t>
         </is>
       </c>
     </row>

--- a/lot_01.xlsx
+++ b/lot_01.xlsx
@@ -27,7 +27,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="11">
+  <fonts count="12">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -85,6 +85,12 @@
       <name val="Calibri"/>
       <color rgb="006B7280"/>
       <sz val="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00111827"/>
+      <sz val="10"/>
     </font>
     <font>
       <name val="Calibri"/>
@@ -147,7 +153,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -213,8 +219,14 @@
     <xf numFmtId="0" fontId="9" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -929,7 +941,11 @@
           <t>Perpignan</t>
         </is>
       </c>
-      <c r="D9" s="17" t="inlineStr"/>
+      <c r="D9" s="23" t="inlineStr">
+        <is>
+          <t>Saint-Laurent-de-la-Salanque (66250)</t>
+        </is>
+      </c>
       <c r="E9" s="18" t="inlineStr">
         <is>
           <t>66</t>
@@ -1292,7 +1308,7 @@
           <t>44</t>
         </is>
       </c>
-      <c r="F7" s="23" t="n">
+      <c r="F7" s="24" t="n">
         <v>47</v>
       </c>
       <c r="G7" s="18" t="n">
@@ -1341,7 +1357,7 @@
           <t>74</t>
         </is>
       </c>
-      <c r="F8" s="23" t="n">
+      <c r="F8" s="24" t="n">
         <v>46</v>
       </c>
       <c r="G8" s="8" t="n">
@@ -1384,13 +1400,17 @@
           <t>Nancy</t>
         </is>
       </c>
-      <c r="D9" s="17" t="inlineStr"/>
+      <c r="D9" s="23" t="inlineStr">
+        <is>
+          <t>Frouard (54390)</t>
+        </is>
+      </c>
       <c r="E9" s="18" t="inlineStr">
         <is>
           <t>54</t>
         </is>
       </c>
-      <c r="F9" s="23" t="n">
+      <c r="F9" s="24" t="n">
         <v>46</v>
       </c>
       <c r="G9" s="18" t="n">
@@ -1433,13 +1453,17 @@
           <t>Lyon</t>
         </is>
       </c>
-      <c r="D10" s="7" t="inlineStr"/>
+      <c r="D10" s="25" t="inlineStr">
+        <is>
+          <t>Pusignan (69330)</t>
+        </is>
+      </c>
       <c r="E10" s="8" t="inlineStr">
         <is>
           <t>69</t>
         </is>
       </c>
-      <c r="F10" s="23" t="n">
+      <c r="F10" s="24" t="n">
         <v>46</v>
       </c>
       <c r="G10" s="8" t="n">
@@ -1747,7 +1771,7 @@
           <t>29</t>
         </is>
       </c>
-      <c r="F7" s="23" t="n">
+      <c r="F7" s="24" t="n">
         <v>49</v>
       </c>
       <c r="G7" s="18" t="n">
@@ -1790,13 +1814,17 @@
           <t>Paris</t>
         </is>
       </c>
-      <c r="D8" s="7" t="inlineStr"/>
+      <c r="D8" s="25" t="inlineStr">
+        <is>
+          <t>Versailles (78000)</t>
+        </is>
+      </c>
       <c r="E8" s="8" t="inlineStr">
         <is>
           <t>75</t>
         </is>
       </c>
-      <c r="F8" s="23" t="n">
+      <c r="F8" s="24" t="n">
         <v>46</v>
       </c>
       <c r="G8" s="8" t="n">
@@ -1839,13 +1867,17 @@
           <t>Limoges</t>
         </is>
       </c>
-      <c r="D9" s="17" t="inlineStr"/>
+      <c r="D9" s="23" t="inlineStr">
+        <is>
+          <t>Saint-Leonard-de-Noblat (87400)</t>
+        </is>
+      </c>
       <c r="E9" s="18" t="inlineStr">
         <is>
           <t>87</t>
         </is>
       </c>
-      <c r="F9" s="23" t="n">
+      <c r="F9" s="24" t="n">
         <v>46</v>
       </c>
       <c r="G9" s="18" t="n">
@@ -1894,7 +1926,7 @@
           <t>59</t>
         </is>
       </c>
-      <c r="F10" s="23" t="n">
+      <c r="F10" s="24" t="n">
         <v>45</v>
       </c>
       <c r="G10" s="8" t="n">
@@ -2147,13 +2179,17 @@
           <t>Perpignan</t>
         </is>
       </c>
-      <c r="D6" s="7" t="inlineStr"/>
+      <c r="D6" s="25" t="inlineStr">
+        <is>
+          <t>Rivesaltes (66600)</t>
+        </is>
+      </c>
       <c r="E6" s="8" t="inlineStr">
         <is>
           <t>66</t>
         </is>
       </c>
-      <c r="F6" s="23" t="n">
+      <c r="F6" s="24" t="n">
         <v>46</v>
       </c>
       <c r="G6" s="8" t="n">
@@ -2196,13 +2232,17 @@
           <t>Saint-Etienne</t>
         </is>
       </c>
-      <c r="D7" s="17" t="inlineStr"/>
+      <c r="D7" s="23" t="inlineStr">
+        <is>
+          <t>La Ricamarie (42150)</t>
+        </is>
+      </c>
       <c r="E7" s="18" t="inlineStr">
         <is>
           <t>42</t>
         </is>
       </c>
-      <c r="F7" s="23" t="n">
+      <c r="F7" s="24" t="n">
         <v>46</v>
       </c>
       <c r="G7" s="18" t="n">
@@ -2245,13 +2285,17 @@
           <t>Nancy</t>
         </is>
       </c>
-      <c r="D8" s="7" t="inlineStr"/>
+      <c r="D8" s="25" t="inlineStr">
+        <is>
+          <t>Toul (54200)</t>
+        </is>
+      </c>
       <c r="E8" s="8" t="inlineStr">
         <is>
           <t>54</t>
         </is>
       </c>
-      <c r="F8" s="23" t="n">
+      <c r="F8" s="24" t="n">
         <v>46</v>
       </c>
       <c r="G8" s="8" t="n">
@@ -2294,13 +2338,17 @@
           <t>Paris</t>
         </is>
       </c>
-      <c r="D9" s="17" t="inlineStr"/>
+      <c r="D9" s="23" t="inlineStr">
+        <is>
+          <t>Le Perreux-sur-Marne (94170)</t>
+        </is>
+      </c>
       <c r="E9" s="18" t="inlineStr">
         <is>
           <t>75</t>
         </is>
       </c>
-      <c r="F9" s="23" t="n">
+      <c r="F9" s="24" t="n">
         <v>46</v>
       </c>
       <c r="G9" s="18" t="n">
@@ -2343,13 +2391,17 @@
           <t>Lyon</t>
         </is>
       </c>
-      <c r="D10" s="7" t="inlineStr"/>
+      <c r="D10" s="25" t="inlineStr">
+        <is>
+          <t>Saint-Bonnet-de-Mure (69720)</t>
+        </is>
+      </c>
       <c r="E10" s="8" t="inlineStr">
         <is>
           <t>69</t>
         </is>
       </c>
-      <c r="F10" s="23" t="n">
+      <c r="F10" s="24" t="n">
         <v>42</v>
       </c>
       <c r="G10" s="8" t="n">
@@ -2504,7 +2556,11 @@
           <t>Paris</t>
         </is>
       </c>
-      <c r="D4" s="7" t="inlineStr"/>
+      <c r="D4" s="25" t="inlineStr">
+        <is>
+          <t>Villeneuve-Saint-Georges (94190)</t>
+        </is>
+      </c>
       <c r="E4" s="8" t="inlineStr">
         <is>
           <t>75</t>
@@ -2553,7 +2609,11 @@
           <t>La Rochelle</t>
         </is>
       </c>
-      <c r="D5" s="17" t="inlineStr"/>
+      <c r="D5" s="23" t="inlineStr">
+        <is>
+          <t>L'Houmeau (17137)</t>
+        </is>
+      </c>
       <c r="E5" s="18" t="inlineStr">
         <is>
           <t>17</t>
@@ -2608,7 +2668,7 @@
           <t>38</t>
         </is>
       </c>
-      <c r="F6" s="23" t="n">
+      <c r="F6" s="24" t="n">
         <v>49</v>
       </c>
       <c r="G6" s="8" t="n">
@@ -2651,13 +2711,17 @@
           <t>Nancy</t>
         </is>
       </c>
-      <c r="D7" s="17" t="inlineStr"/>
+      <c r="D7" s="23" t="inlineStr">
+        <is>
+          <t>Champigneulles (54250)</t>
+        </is>
+      </c>
       <c r="E7" s="18" t="inlineStr">
         <is>
           <t>54</t>
         </is>
       </c>
-      <c r="F7" s="23" t="n">
+      <c r="F7" s="24" t="n">
         <v>46</v>
       </c>
       <c r="G7" s="18" t="n">
@@ -2700,13 +2764,17 @@
           <t>Paris</t>
         </is>
       </c>
-      <c r="D8" s="7" t="inlineStr"/>
+      <c r="D8" s="25" t="inlineStr">
+        <is>
+          <t>Houilles (78800)</t>
+        </is>
+      </c>
       <c r="E8" s="8" t="inlineStr">
         <is>
           <t>75</t>
         </is>
       </c>
-      <c r="F8" s="23" t="n">
+      <c r="F8" s="24" t="n">
         <v>44</v>
       </c>
       <c r="G8" s="8" t="n">
@@ -2755,7 +2823,7 @@
           <t>72</t>
         </is>
       </c>
-      <c r="F9" s="23" t="n">
+      <c r="F9" s="24" t="n">
         <v>42</v>
       </c>
       <c r="G9" s="18" t="n">
@@ -2804,7 +2872,7 @@
           <t>75</t>
         </is>
       </c>
-      <c r="F10" s="23" t="n">
+      <c r="F10" s="24" t="n">
         <v>37</v>
       </c>
       <c r="G10" s="8" t="n">

--- a/lot_01.xlsx
+++ b/lot_01.xlsx
@@ -219,13 +219,13 @@
     <xf numFmtId="0" fontId="9" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -781,23 +781,23 @@
     <row r="6" ht="30" customHeight="1">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>atie-bat.fr</t>
+          <t>biasini-electricite.com</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>Atie Bat</t>
+          <t>Biasini</t>
         </is>
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>Paris</t>
+          <t>Toulouse</t>
         </is>
       </c>
       <c r="D6" s="7" t="inlineStr"/>
       <c r="E6" s="8" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>31</t>
         </is>
       </c>
       <c r="F6" s="9" t="n">
@@ -823,30 +823,30 @@
       </c>
       <c r="K6" s="13" t="inlineStr">
         <is>
-          <t>balises &lt;font&gt; (2) | non responsive | pas de @media | pas de flex/grid | pas de variables CSS | CSS tres court (434B) | aucun radius/ombre</t>
+          <t>balises &lt;font&gt; (1) | non responsive | pas de @media | pas de flex/grid | pas de variables CSS | CSS tres court (434B) | aucun radius/ombre</t>
         </is>
       </c>
     </row>
     <row r="7" ht="30" customHeight="1">
       <c r="A7" s="14" t="inlineStr">
         <is>
-          <t>biasini-electricite.com</t>
+          <t>tech-plomberie.fr</t>
         </is>
       </c>
       <c r="B7" s="15" t="inlineStr">
         <is>
-          <t>Biasini</t>
+          <t>Tec Plomberie</t>
         </is>
       </c>
       <c r="C7" s="16" t="inlineStr">
         <is>
-          <t>Toulouse</t>
+          <t>Orleans</t>
         </is>
       </c>
       <c r="D7" s="17" t="inlineStr"/>
       <c r="E7" s="18" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>45</t>
         </is>
       </c>
       <c r="F7" s="9" t="n">
@@ -872,37 +872,41 @@
       </c>
       <c r="K7" s="22" t="inlineStr">
         <is>
-          <t>balises &lt;font&gt; (1) | non responsive | pas de @media | pas de flex/grid | pas de variables CSS | CSS tres court (434B) | aucun radius/ombre</t>
+          <t>balises &lt;font&gt; (3) | non responsive | pas de @media | pas de flex/grid | pas de variables CSS | CSS tres court (434B) | aucun radius/ombre</t>
         </is>
       </c>
     </row>
     <row r="8" ht="30" customHeight="1">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>tech-plomberie.fr</t>
+          <t>espace-bois-66.com</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>Tec Plomberie</t>
+          <t>Espace Bois Alu PVC</t>
         </is>
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>Orleans</t>
-        </is>
-      </c>
-      <c r="D8" s="7" t="inlineStr"/>
+          <t>Perpignan</t>
+        </is>
+      </c>
+      <c r="D8" s="23" t="inlineStr">
+        <is>
+          <t>Saint-Laurent-de-la-Salanque (66250)</t>
+        </is>
+      </c>
       <c r="E8" s="8" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>66</t>
         </is>
       </c>
       <c r="F8" s="9" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G8" s="8" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H8" s="10" t="inlineStr">
         <is>
@@ -916,46 +920,42 @@
       </c>
       <c r="J8" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>cfirsty®</t>
         </is>
       </c>
       <c r="K8" s="13" t="inlineStr">
         <is>
-          <t>balises &lt;font&gt; (3) | non responsive | pas de @media | pas de flex/grid | pas de variables CSS | CSS tres court (434B) | aucun radius/ombre</t>
+          <t>layout en tableaux (9) | non responsive | pas de @media | pas de flex/grid | pas de variables CSS | police vintage</t>
         </is>
       </c>
     </row>
     <row r="9" ht="30" customHeight="1">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>espace-bois-66.com</t>
+          <t>fais-ci-fais-ca.com</t>
         </is>
       </c>
       <c r="B9" s="15" t="inlineStr">
         <is>
-          <t>Espace Bois Alu PVC</t>
+          <t>Fais ci Fais ça</t>
         </is>
       </c>
       <c r="C9" s="16" t="inlineStr">
         <is>
-          <t>Perpignan</t>
-        </is>
-      </c>
-      <c r="D9" s="23" t="inlineStr">
-        <is>
-          <t>Saint-Laurent-de-la-Salanque (66250)</t>
-        </is>
-      </c>
+          <t>Paris</t>
+        </is>
+      </c>
+      <c r="D9" s="17" t="inlineStr"/>
       <c r="E9" s="18" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>75</t>
         </is>
       </c>
       <c r="F9" s="9" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G9" s="18" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="H9" s="19" t="inlineStr">
         <is>
@@ -969,42 +969,46 @@
       </c>
       <c r="J9" s="21" t="inlineStr">
         <is>
-          <t>cfirsty®</t>
+          <t>wordpress 3.0.1</t>
         </is>
       </c>
       <c r="K9" s="22" t="inlineStr">
         <is>
-          <t>layout en tableaux (9) | non responsive | pas de @media | pas de flex/grid | pas de variables CSS | police vintage</t>
+          <t>&lt;center&gt; | doctype ancien | non responsive | document.write | pas de @media | pas de flex/grid | pas de variables CSS | police vintage</t>
         </is>
       </c>
     </row>
     <row r="10" ht="30" customHeight="1">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>fais-ci-fais-ca.com</t>
+          <t>lorconcept-toiture.com</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>Fais ci Fais ça</t>
+          <t>Lor'Concept Toiture</t>
         </is>
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>Paris</t>
-        </is>
-      </c>
-      <c r="D10" s="7" t="inlineStr"/>
+          <t>Nancy</t>
+        </is>
+      </c>
+      <c r="D10" s="23" t="inlineStr">
+        <is>
+          <t>Tomblaine (54510)</t>
+        </is>
+      </c>
       <c r="E10" s="8" t="inlineStr">
         <is>
-          <t>75</t>
-        </is>
-      </c>
-      <c r="F10" s="9" t="n">
-        <v>54</v>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="F10" s="24" t="n">
+        <v>38</v>
       </c>
       <c r="G10" s="8" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="H10" s="10" t="inlineStr">
         <is>
@@ -1018,12 +1022,12 @@
       </c>
       <c r="J10" s="12" t="inlineStr">
         <is>
-          <t>wordpress 3.0.1</t>
+          <t>—</t>
         </is>
       </c>
       <c r="K10" s="13" t="inlineStr">
         <is>
-          <t>&lt;center&gt; | doctype ancien | non responsive | document.write | pas de @media | pas de flex/grid | pas de variables CSS | police vintage</t>
+          <t>doctype ancien | non responsive | pas de @media | pas de flex/grid</t>
         </is>
       </c>
     </row>
@@ -1400,7 +1404,7 @@
           <t>Nancy</t>
         </is>
       </c>
-      <c r="D9" s="23" t="inlineStr">
+      <c r="D9" s="25" t="inlineStr">
         <is>
           <t>Frouard (54390)</t>
         </is>
@@ -1453,7 +1457,7 @@
           <t>Lyon</t>
         </is>
       </c>
-      <c r="D10" s="25" t="inlineStr">
+      <c r="D10" s="23" t="inlineStr">
         <is>
           <t>Pusignan (69330)</t>
         </is>
@@ -1654,79 +1658,79 @@
     <row r="5" ht="30" customHeight="1">
       <c r="A5" s="14" t="inlineStr">
         <is>
-          <t>chezmario.fr</t>
+          <t>azur-traiteur.fr</t>
         </is>
       </c>
       <c r="B5" s="15" t="inlineStr">
         <is>
-          <t>Chez Mario</t>
+          <t>Azur Traiteur</t>
         </is>
       </c>
       <c r="C5" s="16" t="inlineStr">
         <is>
-          <t>Bordeaux</t>
+          <t>Aix-en-Provence</t>
         </is>
       </c>
       <c r="D5" s="17" t="inlineStr"/>
       <c r="E5" s="18" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>13</t>
         </is>
       </c>
       <c r="F5" s="9" t="n">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="G5" s="18" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="H5" s="19" t="inlineStr">
         <is>
           <t>non</t>
         </is>
       </c>
-      <c r="I5" s="19" t="inlineStr">
-        <is>
-          <t>non</t>
+      <c r="I5" s="20" t="inlineStr">
+        <is>
+          <t>oui</t>
         </is>
       </c>
       <c r="J5" s="21" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>joomla! 1.5 - open source content management</t>
         </is>
       </c>
       <c r="K5" s="22" t="inlineStr">
         <is>
-          <t>layout en tableaux (4) | doctype ancien | non responsive | pas de @media | pas de flex/grid | pas de variables CSS | aucun radius/ombre</t>
+          <t>layout en tableaux (7) | doctype ancien | non responsive | pas de @media | pas de flex/grid</t>
         </is>
       </c>
     </row>
     <row r="6" ht="30" customHeight="1">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>azur-traiteur.fr</t>
+          <t>happy-pizz.com</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>Azur Traiteur</t>
+          <t>Happy Pizz - Chez Jo</t>
         </is>
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>Aix-en-Provence</t>
+          <t>Quimper</t>
         </is>
       </c>
       <c r="D6" s="7" t="inlineStr"/>
       <c r="E6" s="8" t="inlineStr">
         <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="F6" s="9" t="n">
-        <v>52</v>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="F6" s="24" t="n">
+        <v>49</v>
       </c>
       <c r="G6" s="8" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="H6" s="10" t="inlineStr">
         <is>
@@ -1740,42 +1744,46 @@
       </c>
       <c r="J6" s="12" t="inlineStr">
         <is>
-          <t>joomla! 1.5 - open source content management</t>
+          <t>—</t>
         </is>
       </c>
       <c r="K6" s="13" t="inlineStr">
         <is>
-          <t>layout en tableaux (7) | doctype ancien | non responsive | pas de @media | pas de flex/grid</t>
+          <t>bgcolor= | doctype ancien | non responsive | pas de @media | pas de flex/grid | pas de variables CSS | aucun radius/ombre</t>
         </is>
       </c>
     </row>
     <row r="7" ht="30" customHeight="1">
       <c r="A7" s="14" t="inlineStr">
         <is>
-          <t>happy-pizz.com</t>
+          <t>boucherie-economique.fr</t>
         </is>
       </c>
       <c r="B7" s="15" t="inlineStr">
         <is>
-          <t>Happy Pizz - Chez Jo</t>
+          <t>La boucherie économique</t>
         </is>
       </c>
       <c r="C7" s="16" t="inlineStr">
         <is>
-          <t>Quimper</t>
-        </is>
-      </c>
-      <c r="D7" s="17" t="inlineStr"/>
+          <t>Paris</t>
+        </is>
+      </c>
+      <c r="D7" s="25" t="inlineStr">
+        <is>
+          <t>Versailles (78000)</t>
+        </is>
+      </c>
       <c r="E7" s="18" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>75</t>
         </is>
       </c>
       <c r="F7" s="24" t="n">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="G7" s="18" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H7" s="19" t="inlineStr">
         <is>
@@ -1794,34 +1802,34 @@
       </c>
       <c r="K7" s="22" t="inlineStr">
         <is>
-          <t>bgcolor= | doctype ancien | non responsive | pas de @media | pas de flex/grid | pas de variables CSS | aucun radius/ombre</t>
+          <t>non responsive | pas de @media | pas de flex/grid | pas de variables CSS | CSS tres court (434B) | aucun radius/ombre</t>
         </is>
       </c>
     </row>
     <row r="8" ht="30" customHeight="1">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>boucherie-economique.fr</t>
+          <t>coignacsarl.site-solocal.com</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>La boucherie économique</t>
+          <t>Maison Coignac</t>
         </is>
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>Paris</t>
-        </is>
-      </c>
-      <c r="D8" s="25" t="inlineStr">
-        <is>
-          <t>Versailles (78000)</t>
+          <t>Limoges</t>
+        </is>
+      </c>
+      <c r="D8" s="23" t="inlineStr">
+        <is>
+          <t>Saint-Leonard-de-Noblat (87400)</t>
         </is>
       </c>
       <c r="E8" s="8" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>87</t>
         </is>
       </c>
       <c r="F8" s="24" t="n">
@@ -1854,34 +1862,34 @@
     <row r="9" ht="30" customHeight="1">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>coignacsarl.site-solocal.com</t>
+          <t>cafedesarts.alwaysdata.net</t>
         </is>
       </c>
       <c r="B9" s="15" t="inlineStr">
         <is>
-          <t>Maison Coignac</t>
+          <t>Café des Arts</t>
         </is>
       </c>
       <c r="C9" s="16" t="inlineStr">
         <is>
-          <t>Limoges</t>
-        </is>
-      </c>
-      <c r="D9" s="23" t="inlineStr">
-        <is>
-          <t>Saint-Leonard-de-Noblat (87400)</t>
+          <t>Caen</t>
+        </is>
+      </c>
+      <c r="D9" s="25" t="inlineStr">
+        <is>
+          <t>Herouville-Saint-Clair (14200)</t>
         </is>
       </c>
       <c r="E9" s="18" t="inlineStr">
         <is>
-          <t>87</t>
+          <t>14</t>
         </is>
       </c>
       <c r="F9" s="24" t="n">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="G9" s="18" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H9" s="19" t="inlineStr">
         <is>
@@ -1900,46 +1908,46 @@
       </c>
       <c r="K9" s="22" t="inlineStr">
         <is>
-          <t>non responsive | pas de @media | pas de flex/grid | pas de variables CSS | CSS tres court (434B) | aucun radius/ombre</t>
+          <t>&lt;center&gt; | non responsive | pas de @media | pas de flex/grid | pas de variables CSS</t>
         </is>
       </c>
     </row>
     <row r="10" ht="30" customHeight="1">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>chapitre6.fr</t>
+          <t>restaurant-ariana.com</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>Chapitre VI</t>
+          <t>L'Ariana</t>
         </is>
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>Lille</t>
+          <t>Nantes</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr"/>
       <c r="E10" s="8" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>44</t>
         </is>
       </c>
       <c r="F10" s="24" t="n">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="G10" s="8" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="H10" s="10" t="inlineStr">
         <is>
           <t>non</t>
         </is>
       </c>
-      <c r="I10" s="10" t="inlineStr">
-        <is>
-          <t>non</t>
+      <c r="I10" s="11" t="inlineStr">
+        <is>
+          <t>oui</t>
         </is>
       </c>
       <c r="J10" s="12" t="inlineStr">
@@ -1949,7 +1957,7 @@
       </c>
       <c r="K10" s="13" t="inlineStr">
         <is>
-          <t>balises &lt;font&gt; (1) | bgcolor= | frameset | sans doctype | non responsive</t>
+          <t>balises &lt;font&gt; (1) | non responsive | pas de @media</t>
         </is>
       </c>
     </row>
@@ -2179,7 +2187,7 @@
           <t>Perpignan</t>
         </is>
       </c>
-      <c r="D6" s="25" t="inlineStr">
+      <c r="D6" s="23" t="inlineStr">
         <is>
           <t>Rivesaltes (66600)</t>
         </is>
@@ -2232,7 +2240,7 @@
           <t>Saint-Etienne</t>
         </is>
       </c>
-      <c r="D7" s="23" t="inlineStr">
+      <c r="D7" s="25" t="inlineStr">
         <is>
           <t>La Ricamarie (42150)</t>
         </is>
@@ -2285,7 +2293,7 @@
           <t>Nancy</t>
         </is>
       </c>
-      <c r="D8" s="25" t="inlineStr">
+      <c r="D8" s="23" t="inlineStr">
         <is>
           <t>Toul (54200)</t>
         </is>
@@ -2338,7 +2346,7 @@
           <t>Paris</t>
         </is>
       </c>
-      <c r="D9" s="23" t="inlineStr">
+      <c r="D9" s="25" t="inlineStr">
         <is>
           <t>Le Perreux-sur-Marne (94170)</t>
         </is>
@@ -2391,7 +2399,7 @@
           <t>Lyon</t>
         </is>
       </c>
-      <c r="D10" s="25" t="inlineStr">
+      <c r="D10" s="23" t="inlineStr">
         <is>
           <t>Saint-Bonnet-de-Mure (69720)</t>
         </is>
@@ -2556,7 +2564,7 @@
           <t>Paris</t>
         </is>
       </c>
-      <c r="D4" s="25" t="inlineStr">
+      <c r="D4" s="23" t="inlineStr">
         <is>
           <t>Villeneuve-Saint-Georges (94190)</t>
         </is>
@@ -2609,7 +2617,7 @@
           <t>La Rochelle</t>
         </is>
       </c>
-      <c r="D5" s="23" t="inlineStr">
+      <c r="D5" s="25" t="inlineStr">
         <is>
           <t>L'Houmeau (17137)</t>
         </is>
@@ -2711,7 +2719,7 @@
           <t>Nancy</t>
         </is>
       </c>
-      <c r="D7" s="23" t="inlineStr">
+      <c r="D7" s="25" t="inlineStr">
         <is>
           <t>Champigneulles (54250)</t>
         </is>
@@ -2764,7 +2772,7 @@
           <t>Paris</t>
         </is>
       </c>
-      <c r="D8" s="25" t="inlineStr">
+      <c r="D8" s="23" t="inlineStr">
         <is>
           <t>Houilles (78800)</t>
         </is>
